--- a/Excel Files IPEDS/Trimmed/c2001_trimmed_file.xlsx
+++ b/Excel Files IPEDS/Trimmed/c2001_trimmed_file.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E386"/>
+  <dimension ref="A1:G386"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,6 +451,16 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>crace15</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>crace16</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
           <t>Year</t>
         </is>
       </c>
@@ -469,6 +479,12 @@
         <v>7</v>
       </c>
       <c r="E2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F2" t="n">
+        <v>3</v>
+      </c>
+      <c r="G2" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -486,6 +502,12 @@
         <v>9</v>
       </c>
       <c r="E3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F3" t="n">
+        <v>4</v>
+      </c>
+      <c r="G3" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -503,6 +525,12 @@
         <v>9</v>
       </c>
       <c r="E4" t="n">
+        <v>5</v>
+      </c>
+      <c r="F4" t="n">
+        <v>2</v>
+      </c>
+      <c r="G4" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -520,6 +548,12 @@
         <v>9</v>
       </c>
       <c r="E5" t="n">
+        <v>4</v>
+      </c>
+      <c r="F5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G5" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -537,6 +571,12 @@
         <v>7</v>
       </c>
       <c r="E6" t="n">
+        <v>4</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -554,6 +594,12 @@
         <v>7</v>
       </c>
       <c r="E7" t="n">
+        <v>2</v>
+      </c>
+      <c r="F7" t="n">
+        <v>2</v>
+      </c>
+      <c r="G7" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -571,6 +617,12 @@
         <v>7</v>
       </c>
       <c r="E8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F8" t="n">
+        <v>3</v>
+      </c>
+      <c r="G8" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -588,6 +640,12 @@
         <v>7</v>
       </c>
       <c r="E9" t="n">
+        <v>4</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -605,6 +663,12 @@
         <v>7</v>
       </c>
       <c r="E10" t="n">
+        <v>9</v>
+      </c>
+      <c r="F10" t="n">
+        <v>5</v>
+      </c>
+      <c r="G10" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -622,6 +686,12 @@
         <v>7</v>
       </c>
       <c r="E11" t="n">
+        <v>3</v>
+      </c>
+      <c r="F11" t="n">
+        <v>1</v>
+      </c>
+      <c r="G11" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -639,6 +709,12 @@
         <v>7</v>
       </c>
       <c r="E12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -656,6 +732,12 @@
         <v>7</v>
       </c>
       <c r="E13" t="n">
+        <v>4</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -673,6 +755,12 @@
         <v>9</v>
       </c>
       <c r="E14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -690,6 +778,12 @@
         <v>7</v>
       </c>
       <c r="E15" t="n">
+        <v>3</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -707,6 +801,12 @@
         <v>7</v>
       </c>
       <c r="E16" t="n">
+        <v>7</v>
+      </c>
+      <c r="F16" t="n">
+        <v>2</v>
+      </c>
+      <c r="G16" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -724,6 +824,12 @@
         <v>9</v>
       </c>
       <c r="E17" t="n">
+        <v>3</v>
+      </c>
+      <c r="F17" t="n">
+        <v>1</v>
+      </c>
+      <c r="G17" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -741,6 +847,12 @@
         <v>7</v>
       </c>
       <c r="E18" t="n">
+        <v>3</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -758,6 +870,12 @@
         <v>7</v>
       </c>
       <c r="E19" t="n">
+        <v>1</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -775,6 +893,12 @@
         <v>9</v>
       </c>
       <c r="E20" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -792,6 +916,12 @@
         <v>7</v>
       </c>
       <c r="E21" t="n">
+        <v>1</v>
+      </c>
+      <c r="F21" t="n">
+        <v>1</v>
+      </c>
+      <c r="G21" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -809,6 +939,12 @@
         <v>7</v>
       </c>
       <c r="E22" t="n">
+        <v>10</v>
+      </c>
+      <c r="F22" t="n">
+        <v>1</v>
+      </c>
+      <c r="G22" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -826,6 +962,12 @@
         <v>9</v>
       </c>
       <c r="E23" t="n">
+        <v>6</v>
+      </c>
+      <c r="F23" t="n">
+        <v>1</v>
+      </c>
+      <c r="G23" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -843,6 +985,12 @@
         <v>7</v>
       </c>
       <c r="E24" t="n">
+        <v>5</v>
+      </c>
+      <c r="F24" t="n">
+        <v>3</v>
+      </c>
+      <c r="G24" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -860,6 +1008,12 @@
         <v>9</v>
       </c>
       <c r="E25" t="n">
+        <v>3</v>
+      </c>
+      <c r="F25" t="n">
+        <v>1</v>
+      </c>
+      <c r="G25" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -877,6 +1031,12 @@
         <v>7</v>
       </c>
       <c r="E26" t="n">
+        <v>5</v>
+      </c>
+      <c r="F26" t="n">
+        <v>0</v>
+      </c>
+      <c r="G26" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -894,6 +1054,12 @@
         <v>7</v>
       </c>
       <c r="E27" t="n">
+        <v>0</v>
+      </c>
+      <c r="F27" t="n">
+        <v>1</v>
+      </c>
+      <c r="G27" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -911,6 +1077,12 @@
         <v>9</v>
       </c>
       <c r="E28" t="n">
+        <v>5</v>
+      </c>
+      <c r="F28" t="n">
+        <v>0</v>
+      </c>
+      <c r="G28" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -928,6 +1100,12 @@
         <v>7</v>
       </c>
       <c r="E29" t="n">
+        <v>6</v>
+      </c>
+      <c r="F29" t="n">
+        <v>0</v>
+      </c>
+      <c r="G29" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -945,6 +1123,12 @@
         <v>7</v>
       </c>
       <c r="E30" t="n">
+        <v>6</v>
+      </c>
+      <c r="F30" t="n">
+        <v>0</v>
+      </c>
+      <c r="G30" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -962,6 +1146,12 @@
         <v>7</v>
       </c>
       <c r="E31" t="n">
+        <v>1</v>
+      </c>
+      <c r="F31" t="n">
+        <v>0</v>
+      </c>
+      <c r="G31" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -979,6 +1169,12 @@
         <v>7</v>
       </c>
       <c r="E32" t="n">
+        <v>6</v>
+      </c>
+      <c r="F32" t="n">
+        <v>5</v>
+      </c>
+      <c r="G32" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -996,6 +1192,12 @@
         <v>9</v>
       </c>
       <c r="E33" t="n">
+        <v>3</v>
+      </c>
+      <c r="F33" t="n">
+        <v>0</v>
+      </c>
+      <c r="G33" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -1013,6 +1215,12 @@
         <v>7</v>
       </c>
       <c r="E34" t="n">
+        <v>3</v>
+      </c>
+      <c r="F34" t="n">
+        <v>0</v>
+      </c>
+      <c r="G34" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -1030,6 +1238,12 @@
         <v>9</v>
       </c>
       <c r="E35" t="n">
+        <v>6</v>
+      </c>
+      <c r="F35" t="n">
+        <v>2</v>
+      </c>
+      <c r="G35" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -1047,6 +1261,12 @@
         <v>7</v>
       </c>
       <c r="E36" t="n">
+        <v>21</v>
+      </c>
+      <c r="F36" t="n">
+        <v>3</v>
+      </c>
+      <c r="G36" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -1064,6 +1284,12 @@
         <v>9</v>
       </c>
       <c r="E37" t="n">
+        <v>14</v>
+      </c>
+      <c r="F37" t="n">
+        <v>0</v>
+      </c>
+      <c r="G37" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -1081,6 +1307,12 @@
         <v>7</v>
       </c>
       <c r="E38" t="n">
+        <v>10</v>
+      </c>
+      <c r="F38" t="n">
+        <v>2</v>
+      </c>
+      <c r="G38" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -1098,6 +1330,12 @@
         <v>9</v>
       </c>
       <c r="E39" t="n">
+        <v>7</v>
+      </c>
+      <c r="F39" t="n">
+        <v>3</v>
+      </c>
+      <c r="G39" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -1115,6 +1353,12 @@
         <v>7</v>
       </c>
       <c r="E40" t="n">
+        <v>2</v>
+      </c>
+      <c r="F40" t="n">
+        <v>0</v>
+      </c>
+      <c r="G40" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -1132,6 +1376,12 @@
         <v>9</v>
       </c>
       <c r="E41" t="n">
+        <v>6</v>
+      </c>
+      <c r="F41" t="n">
+        <v>2</v>
+      </c>
+      <c r="G41" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -1149,6 +1399,12 @@
         <v>9</v>
       </c>
       <c r="E42" t="n">
+        <v>2</v>
+      </c>
+      <c r="F42" t="n">
+        <v>0</v>
+      </c>
+      <c r="G42" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -1166,6 +1422,12 @@
         <v>7</v>
       </c>
       <c r="E43" t="n">
+        <v>7</v>
+      </c>
+      <c r="F43" t="n">
+        <v>2</v>
+      </c>
+      <c r="G43" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -1183,6 +1445,12 @@
         <v>9</v>
       </c>
       <c r="E44" t="n">
+        <v>6</v>
+      </c>
+      <c r="F44" t="n">
+        <v>1</v>
+      </c>
+      <c r="G44" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -1200,6 +1468,12 @@
         <v>7</v>
       </c>
       <c r="E45" t="n">
+        <v>21</v>
+      </c>
+      <c r="F45" t="n">
+        <v>6</v>
+      </c>
+      <c r="G45" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -1217,6 +1491,12 @@
         <v>7</v>
       </c>
       <c r="E46" t="n">
+        <v>1</v>
+      </c>
+      <c r="F46" t="n">
+        <v>0</v>
+      </c>
+      <c r="G46" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -1234,6 +1514,12 @@
         <v>7</v>
       </c>
       <c r="E47" t="n">
+        <v>5</v>
+      </c>
+      <c r="F47" t="n">
+        <v>3</v>
+      </c>
+      <c r="G47" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -1251,6 +1537,12 @@
         <v>9</v>
       </c>
       <c r="E48" t="n">
+        <v>6</v>
+      </c>
+      <c r="F48" t="n">
+        <v>0</v>
+      </c>
+      <c r="G48" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -1268,6 +1560,12 @@
         <v>7</v>
       </c>
       <c r="E49" t="n">
+        <v>0</v>
+      </c>
+      <c r="F49" t="n">
+        <v>1</v>
+      </c>
+      <c r="G49" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -1285,6 +1583,12 @@
         <v>7</v>
       </c>
       <c r="E50" t="n">
+        <v>1</v>
+      </c>
+      <c r="F50" t="n">
+        <v>0</v>
+      </c>
+      <c r="G50" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -1302,6 +1606,12 @@
         <v>9</v>
       </c>
       <c r="E51" t="n">
+        <v>5</v>
+      </c>
+      <c r="F51" t="n">
+        <v>0</v>
+      </c>
+      <c r="G51" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -1319,6 +1629,12 @@
         <v>9</v>
       </c>
       <c r="E52" t="n">
+        <v>12</v>
+      </c>
+      <c r="F52" t="n">
+        <v>0</v>
+      </c>
+      <c r="G52" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -1336,6 +1652,12 @@
         <v>7</v>
       </c>
       <c r="E53" t="n">
+        <v>12</v>
+      </c>
+      <c r="F53" t="n">
+        <v>6</v>
+      </c>
+      <c r="G53" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -1353,6 +1675,12 @@
         <v>9</v>
       </c>
       <c r="E54" t="n">
+        <v>9</v>
+      </c>
+      <c r="F54" t="n">
+        <v>4</v>
+      </c>
+      <c r="G54" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -1370,6 +1698,12 @@
         <v>7</v>
       </c>
       <c r="E55" t="n">
+        <v>2</v>
+      </c>
+      <c r="F55" t="n">
+        <v>0</v>
+      </c>
+      <c r="G55" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -1387,6 +1721,12 @@
         <v>9</v>
       </c>
       <c r="E56" t="n">
+        <v>1</v>
+      </c>
+      <c r="F56" t="n">
+        <v>0</v>
+      </c>
+      <c r="G56" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -1404,6 +1744,12 @@
         <v>7</v>
       </c>
       <c r="E57" t="n">
+        <v>17</v>
+      </c>
+      <c r="F57" t="n">
+        <v>3</v>
+      </c>
+      <c r="G57" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -1421,6 +1767,12 @@
         <v>7</v>
       </c>
       <c r="E58" t="n">
+        <v>0</v>
+      </c>
+      <c r="F58" t="n">
+        <v>0</v>
+      </c>
+      <c r="G58" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -1438,6 +1790,12 @@
         <v>7</v>
       </c>
       <c r="E59" t="n">
+        <v>1</v>
+      </c>
+      <c r="F59" t="n">
+        <v>0</v>
+      </c>
+      <c r="G59" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -1455,6 +1813,12 @@
         <v>9</v>
       </c>
       <c r="E60" t="n">
+        <v>1</v>
+      </c>
+      <c r="F60" t="n">
+        <v>0</v>
+      </c>
+      <c r="G60" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -1472,6 +1836,12 @@
         <v>7</v>
       </c>
       <c r="E61" t="n">
+        <v>5</v>
+      </c>
+      <c r="F61" t="n">
+        <v>2</v>
+      </c>
+      <c r="G61" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -1489,6 +1859,12 @@
         <v>9</v>
       </c>
       <c r="E62" t="n">
+        <v>0</v>
+      </c>
+      <c r="F62" t="n">
+        <v>0</v>
+      </c>
+      <c r="G62" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -1506,6 +1882,12 @@
         <v>7</v>
       </c>
       <c r="E63" t="n">
+        <v>5</v>
+      </c>
+      <c r="F63" t="n">
+        <v>3</v>
+      </c>
+      <c r="G63" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -1523,6 +1905,12 @@
         <v>9</v>
       </c>
       <c r="E64" t="n">
+        <v>5</v>
+      </c>
+      <c r="F64" t="n">
+        <v>0</v>
+      </c>
+      <c r="G64" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -1540,6 +1928,12 @@
         <v>7</v>
       </c>
       <c r="E65" t="n">
+        <v>2</v>
+      </c>
+      <c r="F65" t="n">
+        <v>1</v>
+      </c>
+      <c r="G65" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -1557,6 +1951,12 @@
         <v>9</v>
       </c>
       <c r="E66" t="n">
+        <v>4</v>
+      </c>
+      <c r="F66" t="n">
+        <v>1</v>
+      </c>
+      <c r="G66" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -1574,6 +1974,12 @@
         <v>7</v>
       </c>
       <c r="E67" t="n">
+        <v>2</v>
+      </c>
+      <c r="F67" t="n">
+        <v>2</v>
+      </c>
+      <c r="G67" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -1591,6 +1997,12 @@
         <v>9</v>
       </c>
       <c r="E68" t="n">
+        <v>16</v>
+      </c>
+      <c r="F68" t="n">
+        <v>4</v>
+      </c>
+      <c r="G68" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -1608,6 +2020,12 @@
         <v>7</v>
       </c>
       <c r="E69" t="n">
+        <v>2</v>
+      </c>
+      <c r="F69" t="n">
+        <v>1</v>
+      </c>
+      <c r="G69" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -1625,6 +2043,12 @@
         <v>9</v>
       </c>
       <c r="E70" t="n">
+        <v>8</v>
+      </c>
+      <c r="F70" t="n">
+        <v>1</v>
+      </c>
+      <c r="G70" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -1642,6 +2066,12 @@
         <v>9</v>
       </c>
       <c r="E71" t="n">
+        <v>2</v>
+      </c>
+      <c r="F71" t="n">
+        <v>2</v>
+      </c>
+      <c r="G71" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -1659,6 +2089,12 @@
         <v>7</v>
       </c>
       <c r="E72" t="n">
+        <v>0</v>
+      </c>
+      <c r="F72" t="n">
+        <v>1</v>
+      </c>
+      <c r="G72" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -1676,6 +2112,12 @@
         <v>9</v>
       </c>
       <c r="E73" t="n">
+        <v>3</v>
+      </c>
+      <c r="F73" t="n">
+        <v>2</v>
+      </c>
+      <c r="G73" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -1693,6 +2135,12 @@
         <v>7</v>
       </c>
       <c r="E74" t="n">
+        <v>1</v>
+      </c>
+      <c r="F74" t="n">
+        <v>1</v>
+      </c>
+      <c r="G74" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -1710,6 +2158,12 @@
         <v>7</v>
       </c>
       <c r="E75" t="n">
+        <v>2</v>
+      </c>
+      <c r="F75" t="n">
+        <v>0</v>
+      </c>
+      <c r="G75" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -1727,6 +2181,12 @@
         <v>9</v>
       </c>
       <c r="E76" t="n">
+        <v>3</v>
+      </c>
+      <c r="F76" t="n">
+        <v>0</v>
+      </c>
+      <c r="G76" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -1744,6 +2204,12 @@
         <v>7</v>
       </c>
       <c r="E77" t="n">
+        <v>3</v>
+      </c>
+      <c r="F77" t="n">
+        <v>1</v>
+      </c>
+      <c r="G77" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -1761,6 +2227,12 @@
         <v>9</v>
       </c>
       <c r="E78" t="n">
+        <v>3</v>
+      </c>
+      <c r="F78" t="n">
+        <v>0</v>
+      </c>
+      <c r="G78" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -1778,6 +2250,12 @@
         <v>7</v>
       </c>
       <c r="E79" t="n">
+        <v>4</v>
+      </c>
+      <c r="F79" t="n">
+        <v>3</v>
+      </c>
+      <c r="G79" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -1795,6 +2273,12 @@
         <v>9</v>
       </c>
       <c r="E80" t="n">
+        <v>3</v>
+      </c>
+      <c r="F80" t="n">
+        <v>1</v>
+      </c>
+      <c r="G80" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -1812,6 +2296,12 @@
         <v>7</v>
       </c>
       <c r="E81" t="n">
+        <v>2</v>
+      </c>
+      <c r="F81" t="n">
+        <v>0</v>
+      </c>
+      <c r="G81" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -1829,6 +2319,12 @@
         <v>7</v>
       </c>
       <c r="E82" t="n">
+        <v>3</v>
+      </c>
+      <c r="F82" t="n">
+        <v>4</v>
+      </c>
+      <c r="G82" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -1846,6 +2342,12 @@
         <v>9</v>
       </c>
       <c r="E83" t="n">
+        <v>3</v>
+      </c>
+      <c r="F83" t="n">
+        <v>1</v>
+      </c>
+      <c r="G83" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -1863,6 +2365,12 @@
         <v>7</v>
       </c>
       <c r="E84" t="n">
+        <v>0</v>
+      </c>
+      <c r="F84" t="n">
+        <v>0</v>
+      </c>
+      <c r="G84" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -1880,6 +2388,12 @@
         <v>7</v>
       </c>
       <c r="E85" t="n">
+        <v>9</v>
+      </c>
+      <c r="F85" t="n">
+        <v>1</v>
+      </c>
+      <c r="G85" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -1897,6 +2411,12 @@
         <v>9</v>
       </c>
       <c r="E86" t="n">
+        <v>6</v>
+      </c>
+      <c r="F86" t="n">
+        <v>2</v>
+      </c>
+      <c r="G86" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -1914,6 +2434,12 @@
         <v>7</v>
       </c>
       <c r="E87" t="n">
+        <v>3</v>
+      </c>
+      <c r="F87" t="n">
+        <v>0</v>
+      </c>
+      <c r="G87" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -1931,6 +2457,12 @@
         <v>9</v>
       </c>
       <c r="E88" t="n">
+        <v>2</v>
+      </c>
+      <c r="F88" t="n">
+        <v>1</v>
+      </c>
+      <c r="G88" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -1948,6 +2480,12 @@
         <v>7</v>
       </c>
       <c r="E89" t="n">
+        <v>4</v>
+      </c>
+      <c r="F89" t="n">
+        <v>1</v>
+      </c>
+      <c r="G89" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -1965,6 +2503,12 @@
         <v>9</v>
       </c>
       <c r="E90" t="n">
+        <v>2</v>
+      </c>
+      <c r="F90" t="n">
+        <v>0</v>
+      </c>
+      <c r="G90" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -1982,6 +2526,12 @@
         <v>7</v>
       </c>
       <c r="E91" t="n">
+        <v>2</v>
+      </c>
+      <c r="F91" t="n">
+        <v>0</v>
+      </c>
+      <c r="G91" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -1999,6 +2549,12 @@
         <v>9</v>
       </c>
       <c r="E92" t="n">
+        <v>3</v>
+      </c>
+      <c r="F92" t="n">
+        <v>1</v>
+      </c>
+      <c r="G92" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -2016,6 +2572,12 @@
         <v>7</v>
       </c>
       <c r="E93" t="n">
+        <v>0</v>
+      </c>
+      <c r="F93" t="n">
+        <v>0</v>
+      </c>
+      <c r="G93" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -2033,6 +2595,12 @@
         <v>7</v>
       </c>
       <c r="E94" t="n">
+        <v>1</v>
+      </c>
+      <c r="F94" t="n">
+        <v>0</v>
+      </c>
+      <c r="G94" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -2050,6 +2618,12 @@
         <v>7</v>
       </c>
       <c r="E95" t="n">
+        <v>1</v>
+      </c>
+      <c r="F95" t="n">
+        <v>2</v>
+      </c>
+      <c r="G95" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -2067,6 +2641,12 @@
         <v>9</v>
       </c>
       <c r="E96" t="n">
+        <v>2</v>
+      </c>
+      <c r="F96" t="n">
+        <v>0</v>
+      </c>
+      <c r="G96" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -2084,6 +2664,12 @@
         <v>7</v>
       </c>
       <c r="E97" t="n">
+        <v>1</v>
+      </c>
+      <c r="F97" t="n">
+        <v>1</v>
+      </c>
+      <c r="G97" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -2101,6 +2687,12 @@
         <v>7</v>
       </c>
       <c r="E98" t="n">
+        <v>9</v>
+      </c>
+      <c r="F98" t="n">
+        <v>2</v>
+      </c>
+      <c r="G98" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -2118,6 +2710,12 @@
         <v>9</v>
       </c>
       <c r="E99" t="n">
+        <v>8</v>
+      </c>
+      <c r="F99" t="n">
+        <v>1</v>
+      </c>
+      <c r="G99" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -2135,6 +2733,12 @@
         <v>7</v>
       </c>
       <c r="E100" t="n">
+        <v>0</v>
+      </c>
+      <c r="F100" t="n">
+        <v>1</v>
+      </c>
+      <c r="G100" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -2152,6 +2756,12 @@
         <v>7</v>
       </c>
       <c r="E101" t="n">
+        <v>3</v>
+      </c>
+      <c r="F101" t="n">
+        <v>0</v>
+      </c>
+      <c r="G101" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -2169,6 +2779,12 @@
         <v>9</v>
       </c>
       <c r="E102" t="n">
+        <v>1</v>
+      </c>
+      <c r="F102" t="n">
+        <v>1</v>
+      </c>
+      <c r="G102" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -2186,6 +2802,12 @@
         <v>7</v>
       </c>
       <c r="E103" t="n">
+        <v>1</v>
+      </c>
+      <c r="F103" t="n">
+        <v>1</v>
+      </c>
+      <c r="G103" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -2203,6 +2825,12 @@
         <v>9</v>
       </c>
       <c r="E104" t="n">
+        <v>5</v>
+      </c>
+      <c r="F104" t="n">
+        <v>2</v>
+      </c>
+      <c r="G104" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -2220,6 +2848,12 @@
         <v>7</v>
       </c>
       <c r="E105" t="n">
+        <v>1</v>
+      </c>
+      <c r="F105" t="n">
+        <v>0</v>
+      </c>
+      <c r="G105" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -2237,6 +2871,12 @@
         <v>7</v>
       </c>
       <c r="E106" t="n">
+        <v>1</v>
+      </c>
+      <c r="F106" t="n">
+        <v>0</v>
+      </c>
+      <c r="G106" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -2254,6 +2894,12 @@
         <v>9</v>
       </c>
       <c r="E107" t="n">
+        <v>9</v>
+      </c>
+      <c r="F107" t="n">
+        <v>1</v>
+      </c>
+      <c r="G107" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -2271,6 +2917,12 @@
         <v>7</v>
       </c>
       <c r="E108" t="n">
+        <v>11</v>
+      </c>
+      <c r="F108" t="n">
+        <v>4</v>
+      </c>
+      <c r="G108" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -2288,6 +2940,12 @@
         <v>9</v>
       </c>
       <c r="E109" t="n">
+        <v>9</v>
+      </c>
+      <c r="F109" t="n">
+        <v>2</v>
+      </c>
+      <c r="G109" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -2305,6 +2963,12 @@
         <v>7</v>
       </c>
       <c r="E110" t="n">
+        <v>1</v>
+      </c>
+      <c r="F110" t="n">
+        <v>1</v>
+      </c>
+      <c r="G110" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -2322,6 +2986,12 @@
         <v>9</v>
       </c>
       <c r="E111" t="n">
+        <v>2</v>
+      </c>
+      <c r="F111" t="n">
+        <v>0</v>
+      </c>
+      <c r="G111" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -2339,6 +3009,12 @@
         <v>7</v>
       </c>
       <c r="E112" t="n">
+        <v>10</v>
+      </c>
+      <c r="F112" t="n">
+        <v>3</v>
+      </c>
+      <c r="G112" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -2356,6 +3032,12 @@
         <v>7</v>
       </c>
       <c r="E113" t="n">
+        <v>1</v>
+      </c>
+      <c r="F113" t="n">
+        <v>0</v>
+      </c>
+      <c r="G113" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -2373,6 +3055,12 @@
         <v>7</v>
       </c>
       <c r="E114" t="n">
+        <v>4</v>
+      </c>
+      <c r="F114" t="n">
+        <v>1</v>
+      </c>
+      <c r="G114" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -2390,6 +3078,12 @@
         <v>7</v>
       </c>
       <c r="E115" t="n">
+        <v>1</v>
+      </c>
+      <c r="F115" t="n">
+        <v>0</v>
+      </c>
+      <c r="G115" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -2407,6 +3101,12 @@
         <v>9</v>
       </c>
       <c r="E116" t="n">
+        <v>1</v>
+      </c>
+      <c r="F116" t="n">
+        <v>0</v>
+      </c>
+      <c r="G116" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -2424,6 +3124,12 @@
         <v>7</v>
       </c>
       <c r="E117" t="n">
+        <v>4</v>
+      </c>
+      <c r="F117" t="n">
+        <v>2</v>
+      </c>
+      <c r="G117" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -2441,6 +3147,12 @@
         <v>7</v>
       </c>
       <c r="E118" t="n">
+        <v>1</v>
+      </c>
+      <c r="F118" t="n">
+        <v>0</v>
+      </c>
+      <c r="G118" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -2458,6 +3170,12 @@
         <v>9</v>
       </c>
       <c r="E119" t="n">
+        <v>4</v>
+      </c>
+      <c r="F119" t="n">
+        <v>0</v>
+      </c>
+      <c r="G119" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -2475,6 +3193,12 @@
         <v>7</v>
       </c>
       <c r="E120" t="n">
+        <v>6</v>
+      </c>
+      <c r="F120" t="n">
+        <v>1</v>
+      </c>
+      <c r="G120" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -2492,6 +3216,12 @@
         <v>9</v>
       </c>
       <c r="E121" t="n">
+        <v>6</v>
+      </c>
+      <c r="F121" t="n">
+        <v>0</v>
+      </c>
+      <c r="G121" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -2509,6 +3239,12 @@
         <v>7</v>
       </c>
       <c r="E122" t="n">
+        <v>5</v>
+      </c>
+      <c r="F122" t="n">
+        <v>1</v>
+      </c>
+      <c r="G122" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -2526,6 +3262,12 @@
         <v>9</v>
       </c>
       <c r="E123" t="n">
+        <v>32</v>
+      </c>
+      <c r="F123" t="n">
+        <v>3</v>
+      </c>
+      <c r="G123" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -2543,6 +3285,12 @@
         <v>7</v>
       </c>
       <c r="E124" t="n">
+        <v>6</v>
+      </c>
+      <c r="F124" t="n">
+        <v>1</v>
+      </c>
+      <c r="G124" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -2560,6 +3308,12 @@
         <v>9</v>
       </c>
       <c r="E125" t="n">
+        <v>3</v>
+      </c>
+      <c r="F125" t="n">
+        <v>1</v>
+      </c>
+      <c r="G125" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -2577,6 +3331,12 @@
         <v>7</v>
       </c>
       <c r="E126" t="n">
+        <v>14</v>
+      </c>
+      <c r="F126" t="n">
+        <v>1</v>
+      </c>
+      <c r="G126" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -2594,6 +3354,12 @@
         <v>9</v>
       </c>
       <c r="E127" t="n">
+        <v>2</v>
+      </c>
+      <c r="F127" t="n">
+        <v>1</v>
+      </c>
+      <c r="G127" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -2611,6 +3377,12 @@
         <v>7</v>
       </c>
       <c r="E128" t="n">
+        <v>16</v>
+      </c>
+      <c r="F128" t="n">
+        <v>6</v>
+      </c>
+      <c r="G128" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -2628,6 +3400,12 @@
         <v>9</v>
       </c>
       <c r="E129" t="n">
+        <v>18</v>
+      </c>
+      <c r="F129" t="n">
+        <v>4</v>
+      </c>
+      <c r="G129" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -2645,6 +3423,12 @@
         <v>7</v>
       </c>
       <c r="E130" t="n">
+        <v>4</v>
+      </c>
+      <c r="F130" t="n">
+        <v>2</v>
+      </c>
+      <c r="G130" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -2662,6 +3446,12 @@
         <v>9</v>
       </c>
       <c r="E131" t="n">
+        <v>4</v>
+      </c>
+      <c r="F131" t="n">
+        <v>2</v>
+      </c>
+      <c r="G131" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -2679,6 +3469,12 @@
         <v>7</v>
       </c>
       <c r="E132" t="n">
+        <v>0</v>
+      </c>
+      <c r="F132" t="n">
+        <v>0</v>
+      </c>
+      <c r="G132" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -2696,6 +3492,12 @@
         <v>9</v>
       </c>
       <c r="E133" t="n">
+        <v>0</v>
+      </c>
+      <c r="F133" t="n">
+        <v>0</v>
+      </c>
+      <c r="G133" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -2713,6 +3515,12 @@
         <v>7</v>
       </c>
       <c r="E134" t="n">
+        <v>0</v>
+      </c>
+      <c r="F134" t="n">
+        <v>0</v>
+      </c>
+      <c r="G134" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -2730,6 +3538,12 @@
         <v>9</v>
       </c>
       <c r="E135" t="n">
+        <v>0</v>
+      </c>
+      <c r="F135" t="n">
+        <v>2</v>
+      </c>
+      <c r="G135" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -2747,6 +3561,12 @@
         <v>7</v>
       </c>
       <c r="E136" t="n">
+        <v>13</v>
+      </c>
+      <c r="F136" t="n">
+        <v>2</v>
+      </c>
+      <c r="G136" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -2764,6 +3584,12 @@
         <v>9</v>
       </c>
       <c r="E137" t="n">
+        <v>5</v>
+      </c>
+      <c r="F137" t="n">
+        <v>1</v>
+      </c>
+      <c r="G137" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -2781,6 +3607,12 @@
         <v>9</v>
       </c>
       <c r="E138" t="n">
+        <v>2</v>
+      </c>
+      <c r="F138" t="n">
+        <v>0</v>
+      </c>
+      <c r="G138" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -2798,6 +3630,12 @@
         <v>7</v>
       </c>
       <c r="E139" t="n">
+        <v>11</v>
+      </c>
+      <c r="F139" t="n">
+        <v>6</v>
+      </c>
+      <c r="G139" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -2815,6 +3653,12 @@
         <v>9</v>
       </c>
       <c r="E140" t="n">
+        <v>17</v>
+      </c>
+      <c r="F140" t="n">
+        <v>1</v>
+      </c>
+      <c r="G140" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -2832,6 +3676,12 @@
         <v>7</v>
       </c>
       <c r="E141" t="n">
+        <v>19</v>
+      </c>
+      <c r="F141" t="n">
+        <v>7</v>
+      </c>
+      <c r="G141" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -2849,6 +3699,12 @@
         <v>9</v>
       </c>
       <c r="E142" t="n">
+        <v>6</v>
+      </c>
+      <c r="F142" t="n">
+        <v>1</v>
+      </c>
+      <c r="G142" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -2866,6 +3722,12 @@
         <v>7</v>
       </c>
       <c r="E143" t="n">
+        <v>3</v>
+      </c>
+      <c r="F143" t="n">
+        <v>1</v>
+      </c>
+      <c r="G143" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -2883,6 +3745,12 @@
         <v>9</v>
       </c>
       <c r="E144" t="n">
+        <v>3</v>
+      </c>
+      <c r="F144" t="n">
+        <v>0</v>
+      </c>
+      <c r="G144" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -2900,6 +3768,12 @@
         <v>7</v>
       </c>
       <c r="E145" t="n">
+        <v>0</v>
+      </c>
+      <c r="F145" t="n">
+        <v>0</v>
+      </c>
+      <c r="G145" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -2917,6 +3791,12 @@
         <v>9</v>
       </c>
       <c r="E146" t="n">
+        <v>4</v>
+      </c>
+      <c r="F146" t="n">
+        <v>1</v>
+      </c>
+      <c r="G146" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -2934,6 +3814,12 @@
         <v>7</v>
       </c>
       <c r="E147" t="n">
+        <v>3</v>
+      </c>
+      <c r="F147" t="n">
+        <v>1</v>
+      </c>
+      <c r="G147" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -2951,6 +3837,12 @@
         <v>7</v>
       </c>
       <c r="E148" t="n">
+        <v>0</v>
+      </c>
+      <c r="F148" t="n">
+        <v>0</v>
+      </c>
+      <c r="G148" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -2968,6 +3860,12 @@
         <v>7</v>
       </c>
       <c r="E149" t="n">
+        <v>1</v>
+      </c>
+      <c r="F149" t="n">
+        <v>0</v>
+      </c>
+      <c r="G149" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -2985,6 +3883,12 @@
         <v>7</v>
       </c>
       <c r="E150" t="n">
+        <v>5</v>
+      </c>
+      <c r="F150" t="n">
+        <v>2</v>
+      </c>
+      <c r="G150" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -3002,6 +3906,12 @@
         <v>7</v>
       </c>
       <c r="E151" t="n">
+        <v>3</v>
+      </c>
+      <c r="F151" t="n">
+        <v>1</v>
+      </c>
+      <c r="G151" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -3019,6 +3929,12 @@
         <v>9</v>
       </c>
       <c r="E152" t="n">
+        <v>8</v>
+      </c>
+      <c r="F152" t="n">
+        <v>1</v>
+      </c>
+      <c r="G152" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -3036,6 +3952,12 @@
         <v>9</v>
       </c>
       <c r="E153" t="n">
+        <v>2</v>
+      </c>
+      <c r="F153" t="n">
+        <v>3</v>
+      </c>
+      <c r="G153" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -3053,6 +3975,12 @@
         <v>7</v>
       </c>
       <c r="E154" t="n">
+        <v>6</v>
+      </c>
+      <c r="F154" t="n">
+        <v>0</v>
+      </c>
+      <c r="G154" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -3070,6 +3998,12 @@
         <v>7</v>
       </c>
       <c r="E155" t="n">
+        <v>7</v>
+      </c>
+      <c r="F155" t="n">
+        <v>2</v>
+      </c>
+      <c r="G155" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -3087,6 +4021,12 @@
         <v>7</v>
       </c>
       <c r="E156" t="n">
+        <v>0</v>
+      </c>
+      <c r="F156" t="n">
+        <v>0</v>
+      </c>
+      <c r="G156" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -3104,6 +4044,12 @@
         <v>7</v>
       </c>
       <c r="E157" t="n">
+        <v>0</v>
+      </c>
+      <c r="F157" t="n">
+        <v>1</v>
+      </c>
+      <c r="G157" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -3121,6 +4067,12 @@
         <v>9</v>
       </c>
       <c r="E158" t="n">
+        <v>3</v>
+      </c>
+      <c r="F158" t="n">
+        <v>1</v>
+      </c>
+      <c r="G158" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -3138,6 +4090,12 @@
         <v>7</v>
       </c>
       <c r="E159" t="n">
+        <v>1</v>
+      </c>
+      <c r="F159" t="n">
+        <v>0</v>
+      </c>
+      <c r="G159" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -3155,6 +4113,12 @@
         <v>9</v>
       </c>
       <c r="E160" t="n">
+        <v>4</v>
+      </c>
+      <c r="F160" t="n">
+        <v>1</v>
+      </c>
+      <c r="G160" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -3172,6 +4136,12 @@
         <v>7</v>
       </c>
       <c r="E161" t="n">
+        <v>0</v>
+      </c>
+      <c r="F161" t="n">
+        <v>1</v>
+      </c>
+      <c r="G161" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -3189,6 +4159,12 @@
         <v>7</v>
       </c>
       <c r="E162" t="n">
+        <v>5</v>
+      </c>
+      <c r="F162" t="n">
+        <v>0</v>
+      </c>
+      <c r="G162" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -3206,6 +4182,12 @@
         <v>9</v>
       </c>
       <c r="E163" t="n">
+        <v>3</v>
+      </c>
+      <c r="F163" t="n">
+        <v>0</v>
+      </c>
+      <c r="G163" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -3223,6 +4205,12 @@
         <v>7</v>
       </c>
       <c r="E164" t="n">
+        <v>0</v>
+      </c>
+      <c r="F164" t="n">
+        <v>0</v>
+      </c>
+      <c r="G164" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -3240,6 +4228,12 @@
         <v>9</v>
       </c>
       <c r="E165" t="n">
+        <v>1</v>
+      </c>
+      <c r="F165" t="n">
+        <v>0</v>
+      </c>
+      <c r="G165" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -3257,6 +4251,12 @@
         <v>7</v>
       </c>
       <c r="E166" t="n">
+        <v>5</v>
+      </c>
+      <c r="F166" t="n">
+        <v>0</v>
+      </c>
+      <c r="G166" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -3274,6 +4274,12 @@
         <v>9</v>
       </c>
       <c r="E167" t="n">
+        <v>6</v>
+      </c>
+      <c r="F167" t="n">
+        <v>3</v>
+      </c>
+      <c r="G167" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -3291,6 +4297,12 @@
         <v>7</v>
       </c>
       <c r="E168" t="n">
+        <v>10</v>
+      </c>
+      <c r="F168" t="n">
+        <v>2</v>
+      </c>
+      <c r="G168" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -3308,6 +4320,12 @@
         <v>9</v>
       </c>
       <c r="E169" t="n">
+        <v>8</v>
+      </c>
+      <c r="F169" t="n">
+        <v>1</v>
+      </c>
+      <c r="G169" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -3325,6 +4343,12 @@
         <v>7</v>
       </c>
       <c r="E170" t="n">
+        <v>2</v>
+      </c>
+      <c r="F170" t="n">
+        <v>1</v>
+      </c>
+      <c r="G170" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -3342,6 +4366,12 @@
         <v>7</v>
       </c>
       <c r="E171" t="n">
+        <v>2</v>
+      </c>
+      <c r="F171" t="n">
+        <v>0</v>
+      </c>
+      <c r="G171" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -3359,6 +4389,12 @@
         <v>7</v>
       </c>
       <c r="E172" t="n">
+        <v>1</v>
+      </c>
+      <c r="F172" t="n">
+        <v>0</v>
+      </c>
+      <c r="G172" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -3376,6 +4412,12 @@
         <v>7</v>
       </c>
       <c r="E173" t="n">
+        <v>2</v>
+      </c>
+      <c r="F173" t="n">
+        <v>2</v>
+      </c>
+      <c r="G173" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -3393,6 +4435,12 @@
         <v>7</v>
       </c>
       <c r="E174" t="n">
+        <v>5</v>
+      </c>
+      <c r="F174" t="n">
+        <v>1</v>
+      </c>
+      <c r="G174" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -3410,6 +4458,12 @@
         <v>7</v>
       </c>
       <c r="E175" t="n">
+        <v>1</v>
+      </c>
+      <c r="F175" t="n">
+        <v>0</v>
+      </c>
+      <c r="G175" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -3427,6 +4481,12 @@
         <v>7</v>
       </c>
       <c r="E176" t="n">
+        <v>2</v>
+      </c>
+      <c r="F176" t="n">
+        <v>1</v>
+      </c>
+      <c r="G176" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -3444,6 +4504,12 @@
         <v>7</v>
       </c>
       <c r="E177" t="n">
+        <v>0</v>
+      </c>
+      <c r="F177" t="n">
+        <v>1</v>
+      </c>
+      <c r="G177" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -3461,6 +4527,12 @@
         <v>7</v>
       </c>
       <c r="E178" t="n">
+        <v>4</v>
+      </c>
+      <c r="F178" t="n">
+        <v>2</v>
+      </c>
+      <c r="G178" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -3478,6 +4550,12 @@
         <v>9</v>
       </c>
       <c r="E179" t="n">
+        <v>0</v>
+      </c>
+      <c r="F179" t="n">
+        <v>0</v>
+      </c>
+      <c r="G179" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -3495,6 +4573,12 @@
         <v>7</v>
       </c>
       <c r="E180" t="n">
+        <v>3</v>
+      </c>
+      <c r="F180" t="n">
+        <v>0</v>
+      </c>
+      <c r="G180" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -3512,6 +4596,12 @@
         <v>9</v>
       </c>
       <c r="E181" t="n">
+        <v>5</v>
+      </c>
+      <c r="F181" t="n">
+        <v>1</v>
+      </c>
+      <c r="G181" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -3529,6 +4619,12 @@
         <v>9</v>
       </c>
       <c r="E182" t="n">
+        <v>3</v>
+      </c>
+      <c r="F182" t="n">
+        <v>0</v>
+      </c>
+      <c r="G182" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -3546,6 +4642,12 @@
         <v>7</v>
       </c>
       <c r="E183" t="n">
+        <v>27</v>
+      </c>
+      <c r="F183" t="n">
+        <v>5</v>
+      </c>
+      <c r="G183" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -3563,6 +4665,12 @@
         <v>9</v>
       </c>
       <c r="E184" t="n">
+        <v>35</v>
+      </c>
+      <c r="F184" t="n">
+        <v>2</v>
+      </c>
+      <c r="G184" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -3580,6 +4688,12 @@
         <v>7</v>
       </c>
       <c r="E185" t="n">
+        <v>6</v>
+      </c>
+      <c r="F185" t="n">
+        <v>5</v>
+      </c>
+      <c r="G185" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -3597,6 +4711,12 @@
         <v>9</v>
       </c>
       <c r="E186" t="n">
+        <v>3</v>
+      </c>
+      <c r="F186" t="n">
+        <v>0</v>
+      </c>
+      <c r="G186" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -3614,6 +4734,12 @@
         <v>7</v>
       </c>
       <c r="E187" t="n">
+        <v>1</v>
+      </c>
+      <c r="F187" t="n">
+        <v>0</v>
+      </c>
+      <c r="G187" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -3631,6 +4757,12 @@
         <v>7</v>
       </c>
       <c r="E188" t="n">
+        <v>4</v>
+      </c>
+      <c r="F188" t="n">
+        <v>0</v>
+      </c>
+      <c r="G188" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -3648,6 +4780,12 @@
         <v>9</v>
       </c>
       <c r="E189" t="n">
+        <v>12</v>
+      </c>
+      <c r="F189" t="n">
+        <v>1</v>
+      </c>
+      <c r="G189" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -3665,6 +4803,12 @@
         <v>9</v>
       </c>
       <c r="E190" t="n">
+        <v>1</v>
+      </c>
+      <c r="F190" t="n">
+        <v>0</v>
+      </c>
+      <c r="G190" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -3682,6 +4826,12 @@
         <v>7</v>
       </c>
       <c r="E191" t="n">
+        <v>8</v>
+      </c>
+      <c r="F191" t="n">
+        <v>0</v>
+      </c>
+      <c r="G191" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -3699,6 +4849,12 @@
         <v>7</v>
       </c>
       <c r="E192" t="n">
+        <v>1</v>
+      </c>
+      <c r="F192" t="n">
+        <v>0</v>
+      </c>
+      <c r="G192" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -3716,6 +4872,12 @@
         <v>9</v>
       </c>
       <c r="E193" t="n">
+        <v>3</v>
+      </c>
+      <c r="F193" t="n">
+        <v>0</v>
+      </c>
+      <c r="G193" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -3733,6 +4895,12 @@
         <v>7</v>
       </c>
       <c r="E194" t="n">
+        <v>3</v>
+      </c>
+      <c r="F194" t="n">
+        <v>0</v>
+      </c>
+      <c r="G194" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -3750,6 +4918,12 @@
         <v>9</v>
       </c>
       <c r="E195" t="n">
+        <v>8</v>
+      </c>
+      <c r="F195" t="n">
+        <v>1</v>
+      </c>
+      <c r="G195" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -3767,6 +4941,12 @@
         <v>7</v>
       </c>
       <c r="E196" t="n">
+        <v>6</v>
+      </c>
+      <c r="F196" t="n">
+        <v>0</v>
+      </c>
+      <c r="G196" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -3784,6 +4964,12 @@
         <v>7</v>
       </c>
       <c r="E197" t="n">
+        <v>5</v>
+      </c>
+      <c r="F197" t="n">
+        <v>0</v>
+      </c>
+      <c r="G197" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -3801,6 +4987,12 @@
         <v>9</v>
       </c>
       <c r="E198" t="n">
+        <v>9</v>
+      </c>
+      <c r="F198" t="n">
+        <v>1</v>
+      </c>
+      <c r="G198" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -3818,6 +5010,12 @@
         <v>7</v>
       </c>
       <c r="E199" t="n">
+        <v>1</v>
+      </c>
+      <c r="F199" t="n">
+        <v>1</v>
+      </c>
+      <c r="G199" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -3835,6 +5033,12 @@
         <v>7</v>
       </c>
       <c r="E200" t="n">
+        <v>8</v>
+      </c>
+      <c r="F200" t="n">
+        <v>0</v>
+      </c>
+      <c r="G200" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -3852,6 +5056,12 @@
         <v>7</v>
       </c>
       <c r="E201" t="n">
+        <v>2</v>
+      </c>
+      <c r="F201" t="n">
+        <v>0</v>
+      </c>
+      <c r="G201" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -3869,6 +5079,12 @@
         <v>9</v>
       </c>
       <c r="E202" t="n">
+        <v>2</v>
+      </c>
+      <c r="F202" t="n">
+        <v>0</v>
+      </c>
+      <c r="G202" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -3886,6 +5102,12 @@
         <v>7</v>
       </c>
       <c r="E203" t="n">
+        <v>3</v>
+      </c>
+      <c r="F203" t="n">
+        <v>1</v>
+      </c>
+      <c r="G203" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -3903,6 +5125,12 @@
         <v>9</v>
       </c>
       <c r="E204" t="n">
+        <v>12</v>
+      </c>
+      <c r="F204" t="n">
+        <v>1</v>
+      </c>
+      <c r="G204" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -3920,6 +5148,12 @@
         <v>7</v>
       </c>
       <c r="E205" t="n">
+        <v>6</v>
+      </c>
+      <c r="F205" t="n">
+        <v>3</v>
+      </c>
+      <c r="G205" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -3937,6 +5171,12 @@
         <v>7</v>
       </c>
       <c r="E206" t="n">
+        <v>8</v>
+      </c>
+      <c r="F206" t="n">
+        <v>1</v>
+      </c>
+      <c r="G206" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -3954,6 +5194,12 @@
         <v>9</v>
       </c>
       <c r="E207" t="n">
+        <v>6</v>
+      </c>
+      <c r="F207" t="n">
+        <v>3</v>
+      </c>
+      <c r="G207" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -3971,6 +5217,12 @@
         <v>7</v>
       </c>
       <c r="E208" t="n">
+        <v>3</v>
+      </c>
+      <c r="F208" t="n">
+        <v>0</v>
+      </c>
+      <c r="G208" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -3988,6 +5240,12 @@
         <v>9</v>
       </c>
       <c r="E209" t="n">
+        <v>1</v>
+      </c>
+      <c r="F209" t="n">
+        <v>0</v>
+      </c>
+      <c r="G209" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -4005,6 +5263,12 @@
         <v>7</v>
       </c>
       <c r="E210" t="n">
+        <v>7</v>
+      </c>
+      <c r="F210" t="n">
+        <v>2</v>
+      </c>
+      <c r="G210" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -4022,6 +5286,12 @@
         <v>9</v>
       </c>
       <c r="E211" t="n">
+        <v>3</v>
+      </c>
+      <c r="F211" t="n">
+        <v>2</v>
+      </c>
+      <c r="G211" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -4039,6 +5309,12 @@
         <v>7</v>
       </c>
       <c r="E212" t="n">
+        <v>3</v>
+      </c>
+      <c r="F212" t="n">
+        <v>1</v>
+      </c>
+      <c r="G212" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -4056,6 +5332,12 @@
         <v>7</v>
       </c>
       <c r="E213" t="n">
+        <v>1</v>
+      </c>
+      <c r="F213" t="n">
+        <v>1</v>
+      </c>
+      <c r="G213" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -4073,6 +5355,12 @@
         <v>9</v>
       </c>
       <c r="E214" t="n">
+        <v>1</v>
+      </c>
+      <c r="F214" t="n">
+        <v>1</v>
+      </c>
+      <c r="G214" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -4090,6 +5378,12 @@
         <v>7</v>
       </c>
       <c r="E215" t="n">
+        <v>0</v>
+      </c>
+      <c r="F215" t="n">
+        <v>1</v>
+      </c>
+      <c r="G215" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -4107,6 +5401,12 @@
         <v>9</v>
       </c>
       <c r="E216" t="n">
+        <v>1</v>
+      </c>
+      <c r="F216" t="n">
+        <v>2</v>
+      </c>
+      <c r="G216" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -4124,6 +5424,12 @@
         <v>7</v>
       </c>
       <c r="E217" t="n">
+        <v>1</v>
+      </c>
+      <c r="F217" t="n">
+        <v>2</v>
+      </c>
+      <c r="G217" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -4141,6 +5447,12 @@
         <v>9</v>
       </c>
       <c r="E218" t="n">
+        <v>0</v>
+      </c>
+      <c r="F218" t="n">
+        <v>3</v>
+      </c>
+      <c r="G218" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -4158,6 +5470,12 @@
         <v>7</v>
       </c>
       <c r="E219" t="n">
+        <v>3</v>
+      </c>
+      <c r="F219" t="n">
+        <v>0</v>
+      </c>
+      <c r="G219" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -4175,6 +5493,12 @@
         <v>9</v>
       </c>
       <c r="E220" t="n">
+        <v>3</v>
+      </c>
+      <c r="F220" t="n">
+        <v>0</v>
+      </c>
+      <c r="G220" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -4192,6 +5516,12 @@
         <v>7</v>
       </c>
       <c r="E221" t="n">
+        <v>2</v>
+      </c>
+      <c r="F221" t="n">
+        <v>0</v>
+      </c>
+      <c r="G221" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -4209,6 +5539,12 @@
         <v>7</v>
       </c>
       <c r="E222" t="n">
+        <v>1</v>
+      </c>
+      <c r="F222" t="n">
+        <v>1</v>
+      </c>
+      <c r="G222" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -4226,6 +5562,12 @@
         <v>9</v>
       </c>
       <c r="E223" t="n">
+        <v>3</v>
+      </c>
+      <c r="F223" t="n">
+        <v>1</v>
+      </c>
+      <c r="G223" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -4243,6 +5585,12 @@
         <v>7</v>
       </c>
       <c r="E224" t="n">
+        <v>0</v>
+      </c>
+      <c r="F224" t="n">
+        <v>0</v>
+      </c>
+      <c r="G224" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -4260,6 +5608,12 @@
         <v>9</v>
       </c>
       <c r="E225" t="n">
+        <v>0</v>
+      </c>
+      <c r="F225" t="n">
+        <v>0</v>
+      </c>
+      <c r="G225" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -4277,6 +5631,12 @@
         <v>7</v>
       </c>
       <c r="E226" t="n">
+        <v>10</v>
+      </c>
+      <c r="F226" t="n">
+        <v>2</v>
+      </c>
+      <c r="G226" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -4294,6 +5654,12 @@
         <v>9</v>
       </c>
       <c r="E227" t="n">
+        <v>11</v>
+      </c>
+      <c r="F227" t="n">
+        <v>2</v>
+      </c>
+      <c r="G227" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -4311,6 +5677,12 @@
         <v>7</v>
       </c>
       <c r="E228" t="n">
+        <v>0</v>
+      </c>
+      <c r="F228" t="n">
+        <v>0</v>
+      </c>
+      <c r="G228" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -4328,6 +5700,12 @@
         <v>7</v>
       </c>
       <c r="E229" t="n">
+        <v>5</v>
+      </c>
+      <c r="F229" t="n">
+        <v>0</v>
+      </c>
+      <c r="G229" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -4345,6 +5723,12 @@
         <v>9</v>
       </c>
       <c r="E230" t="n">
+        <v>5</v>
+      </c>
+      <c r="F230" t="n">
+        <v>0</v>
+      </c>
+      <c r="G230" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -4362,6 +5746,12 @@
         <v>7</v>
       </c>
       <c r="E231" t="n">
+        <v>0</v>
+      </c>
+      <c r="F231" t="n">
+        <v>0</v>
+      </c>
+      <c r="G231" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -4379,6 +5769,12 @@
         <v>9</v>
       </c>
       <c r="E232" t="n">
+        <v>1</v>
+      </c>
+      <c r="F232" t="n">
+        <v>0</v>
+      </c>
+      <c r="G232" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -4396,6 +5792,12 @@
         <v>7</v>
       </c>
       <c r="E233" t="n">
+        <v>0</v>
+      </c>
+      <c r="F233" t="n">
+        <v>0</v>
+      </c>
+      <c r="G233" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -4413,6 +5815,12 @@
         <v>7</v>
       </c>
       <c r="E234" t="n">
+        <v>2</v>
+      </c>
+      <c r="F234" t="n">
+        <v>2</v>
+      </c>
+      <c r="G234" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -4430,6 +5838,12 @@
         <v>9</v>
       </c>
       <c r="E235" t="n">
+        <v>3</v>
+      </c>
+      <c r="F235" t="n">
+        <v>0</v>
+      </c>
+      <c r="G235" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -4447,6 +5861,12 @@
         <v>7</v>
       </c>
       <c r="E236" t="n">
+        <v>2</v>
+      </c>
+      <c r="F236" t="n">
+        <v>0</v>
+      </c>
+      <c r="G236" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -4464,6 +5884,12 @@
         <v>7</v>
       </c>
       <c r="E237" t="n">
+        <v>6</v>
+      </c>
+      <c r="F237" t="n">
+        <v>2</v>
+      </c>
+      <c r="G237" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -4481,6 +5907,12 @@
         <v>9</v>
       </c>
       <c r="E238" t="n">
+        <v>9</v>
+      </c>
+      <c r="F238" t="n">
+        <v>0</v>
+      </c>
+      <c r="G238" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -4498,6 +5930,12 @@
         <v>7</v>
       </c>
       <c r="E239" t="n">
+        <v>1</v>
+      </c>
+      <c r="F239" t="n">
+        <v>0</v>
+      </c>
+      <c r="G239" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -4515,6 +5953,12 @@
         <v>9</v>
       </c>
       <c r="E240" t="n">
+        <v>5</v>
+      </c>
+      <c r="F240" t="n">
+        <v>0</v>
+      </c>
+      <c r="G240" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -4532,6 +5976,12 @@
         <v>7</v>
       </c>
       <c r="E241" t="n">
+        <v>6</v>
+      </c>
+      <c r="F241" t="n">
+        <v>0</v>
+      </c>
+      <c r="G241" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -4549,6 +5999,12 @@
         <v>7</v>
       </c>
       <c r="E242" t="n">
+        <v>5</v>
+      </c>
+      <c r="F242" t="n">
+        <v>1</v>
+      </c>
+      <c r="G242" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -4566,6 +6022,12 @@
         <v>7</v>
       </c>
       <c r="E243" t="n">
+        <v>5</v>
+      </c>
+      <c r="F243" t="n">
+        <v>0</v>
+      </c>
+      <c r="G243" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -4583,6 +6045,12 @@
         <v>7</v>
       </c>
       <c r="E244" t="n">
+        <v>10</v>
+      </c>
+      <c r="F244" t="n">
+        <v>2</v>
+      </c>
+      <c r="G244" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -4600,6 +6068,12 @@
         <v>9</v>
       </c>
       <c r="E245" t="n">
+        <v>10</v>
+      </c>
+      <c r="F245" t="n">
+        <v>1</v>
+      </c>
+      <c r="G245" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -4617,6 +6091,12 @@
         <v>7</v>
       </c>
       <c r="E246" t="n">
+        <v>7</v>
+      </c>
+      <c r="F246" t="n">
+        <v>2</v>
+      </c>
+      <c r="G246" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -4634,6 +6114,12 @@
         <v>9</v>
       </c>
       <c r="E247" t="n">
+        <v>14</v>
+      </c>
+      <c r="F247" t="n">
+        <v>1</v>
+      </c>
+      <c r="G247" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -4651,6 +6137,12 @@
         <v>7</v>
       </c>
       <c r="E248" t="n">
+        <v>8</v>
+      </c>
+      <c r="F248" t="n">
+        <v>4</v>
+      </c>
+      <c r="G248" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -4668,6 +6160,12 @@
         <v>9</v>
       </c>
       <c r="E249" t="n">
+        <v>5</v>
+      </c>
+      <c r="F249" t="n">
+        <v>2</v>
+      </c>
+      <c r="G249" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -4685,6 +6183,12 @@
         <v>9</v>
       </c>
       <c r="E250" t="n">
+        <v>3</v>
+      </c>
+      <c r="F250" t="n">
+        <v>1</v>
+      </c>
+      <c r="G250" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -4702,6 +6206,12 @@
         <v>7</v>
       </c>
       <c r="E251" t="n">
+        <v>21</v>
+      </c>
+      <c r="F251" t="n">
+        <v>2</v>
+      </c>
+      <c r="G251" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -4719,6 +6229,12 @@
         <v>9</v>
       </c>
       <c r="E252" t="n">
+        <v>17</v>
+      </c>
+      <c r="F252" t="n">
+        <v>2</v>
+      </c>
+      <c r="G252" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -4736,6 +6252,12 @@
         <v>7</v>
       </c>
       <c r="E253" t="n">
+        <v>5</v>
+      </c>
+      <c r="F253" t="n">
+        <v>3</v>
+      </c>
+      <c r="G253" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -4753,6 +6275,12 @@
         <v>9</v>
       </c>
       <c r="E254" t="n">
+        <v>7</v>
+      </c>
+      <c r="F254" t="n">
+        <v>1</v>
+      </c>
+      <c r="G254" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -4770,6 +6298,12 @@
         <v>7</v>
       </c>
       <c r="E255" t="n">
+        <v>22</v>
+      </c>
+      <c r="F255" t="n">
+        <v>5</v>
+      </c>
+      <c r="G255" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -4787,6 +6321,12 @@
         <v>9</v>
       </c>
       <c r="E256" t="n">
+        <v>39</v>
+      </c>
+      <c r="F256" t="n">
+        <v>2</v>
+      </c>
+      <c r="G256" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -4804,6 +6344,12 @@
         <v>7</v>
       </c>
       <c r="E257" t="n">
+        <v>8</v>
+      </c>
+      <c r="F257" t="n">
+        <v>1</v>
+      </c>
+      <c r="G257" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -4821,6 +6367,12 @@
         <v>9</v>
       </c>
       <c r="E258" t="n">
+        <v>13</v>
+      </c>
+      <c r="F258" t="n">
+        <v>2</v>
+      </c>
+      <c r="G258" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -4838,6 +6390,12 @@
         <v>7</v>
       </c>
       <c r="E259" t="n">
+        <v>5</v>
+      </c>
+      <c r="F259" t="n">
+        <v>2</v>
+      </c>
+      <c r="G259" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -4855,6 +6413,12 @@
         <v>7</v>
       </c>
       <c r="E260" t="n">
+        <v>5</v>
+      </c>
+      <c r="F260" t="n">
+        <v>1</v>
+      </c>
+      <c r="G260" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -4872,6 +6436,12 @@
         <v>7</v>
       </c>
       <c r="E261" t="n">
+        <v>3</v>
+      </c>
+      <c r="F261" t="n">
+        <v>0</v>
+      </c>
+      <c r="G261" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -4889,6 +6459,12 @@
         <v>7</v>
       </c>
       <c r="E262" t="n">
+        <v>1</v>
+      </c>
+      <c r="F262" t="n">
+        <v>1</v>
+      </c>
+      <c r="G262" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -4906,6 +6482,12 @@
         <v>7</v>
       </c>
       <c r="E263" t="n">
+        <v>4</v>
+      </c>
+      <c r="F263" t="n">
+        <v>0</v>
+      </c>
+      <c r="G263" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -4923,6 +6505,12 @@
         <v>7</v>
       </c>
       <c r="E264" t="n">
+        <v>1</v>
+      </c>
+      <c r="F264" t="n">
+        <v>0</v>
+      </c>
+      <c r="G264" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -4940,6 +6528,12 @@
         <v>7</v>
       </c>
       <c r="E265" t="n">
+        <v>3</v>
+      </c>
+      <c r="F265" t="n">
+        <v>0</v>
+      </c>
+      <c r="G265" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -4957,6 +6551,12 @@
         <v>9</v>
       </c>
       <c r="E266" t="n">
+        <v>11</v>
+      </c>
+      <c r="F266" t="n">
+        <v>2</v>
+      </c>
+      <c r="G266" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -4974,6 +6574,12 @@
         <v>7</v>
       </c>
       <c r="E267" t="n">
+        <v>1</v>
+      </c>
+      <c r="F267" t="n">
+        <v>0</v>
+      </c>
+      <c r="G267" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -4991,6 +6597,12 @@
         <v>9</v>
       </c>
       <c r="E268" t="n">
+        <v>4</v>
+      </c>
+      <c r="F268" t="n">
+        <v>0</v>
+      </c>
+      <c r="G268" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -5008,6 +6620,12 @@
         <v>7</v>
       </c>
       <c r="E269" t="n">
+        <v>8</v>
+      </c>
+      <c r="F269" t="n">
+        <v>4</v>
+      </c>
+      <c r="G269" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -5025,6 +6643,12 @@
         <v>9</v>
       </c>
       <c r="E270" t="n">
+        <v>5</v>
+      </c>
+      <c r="F270" t="n">
+        <v>0</v>
+      </c>
+      <c r="G270" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -5042,6 +6666,12 @@
         <v>9</v>
       </c>
       <c r="E271" t="n">
+        <v>0</v>
+      </c>
+      <c r="F271" t="n">
+        <v>2</v>
+      </c>
+      <c r="G271" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -5059,6 +6689,12 @@
         <v>7</v>
       </c>
       <c r="E272" t="n">
+        <v>3</v>
+      </c>
+      <c r="F272" t="n">
+        <v>1</v>
+      </c>
+      <c r="G272" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -5076,6 +6712,12 @@
         <v>9</v>
       </c>
       <c r="E273" t="n">
+        <v>4</v>
+      </c>
+      <c r="F273" t="n">
+        <v>1</v>
+      </c>
+      <c r="G273" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -5093,6 +6735,12 @@
         <v>7</v>
       </c>
       <c r="E274" t="n">
+        <v>0</v>
+      </c>
+      <c r="F274" t="n">
+        <v>0</v>
+      </c>
+      <c r="G274" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -5110,6 +6758,12 @@
         <v>7</v>
       </c>
       <c r="E275" t="n">
+        <v>3</v>
+      </c>
+      <c r="F275" t="n">
+        <v>0</v>
+      </c>
+      <c r="G275" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -5127,6 +6781,12 @@
         <v>9</v>
       </c>
       <c r="E276" t="n">
+        <v>1</v>
+      </c>
+      <c r="F276" t="n">
+        <v>0</v>
+      </c>
+      <c r="G276" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -5144,6 +6804,12 @@
         <v>7</v>
       </c>
       <c r="E277" t="n">
+        <v>8</v>
+      </c>
+      <c r="F277" t="n">
+        <v>1</v>
+      </c>
+      <c r="G277" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -5161,6 +6827,12 @@
         <v>9</v>
       </c>
       <c r="E278" t="n">
+        <v>5</v>
+      </c>
+      <c r="F278" t="n">
+        <v>1</v>
+      </c>
+      <c r="G278" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -5178,6 +6850,12 @@
         <v>7</v>
       </c>
       <c r="E279" t="n">
+        <v>2</v>
+      </c>
+      <c r="F279" t="n">
+        <v>1</v>
+      </c>
+      <c r="G279" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -5195,6 +6873,12 @@
         <v>9</v>
       </c>
       <c r="E280" t="n">
+        <v>4</v>
+      </c>
+      <c r="F280" t="n">
+        <v>1</v>
+      </c>
+      <c r="G280" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -5212,6 +6896,12 @@
         <v>9</v>
       </c>
       <c r="E281" t="n">
+        <v>17</v>
+      </c>
+      <c r="F281" t="n">
+        <v>5</v>
+      </c>
+      <c r="G281" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -5229,6 +6919,12 @@
         <v>7</v>
       </c>
       <c r="E282" t="n">
+        <v>5</v>
+      </c>
+      <c r="F282" t="n">
+        <v>2</v>
+      </c>
+      <c r="G282" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -5246,6 +6942,12 @@
         <v>7</v>
       </c>
       <c r="E283" t="n">
+        <v>0</v>
+      </c>
+      <c r="F283" t="n">
+        <v>0</v>
+      </c>
+      <c r="G283" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -5263,6 +6965,12 @@
         <v>9</v>
       </c>
       <c r="E284" t="n">
+        <v>2</v>
+      </c>
+      <c r="F284" t="n">
+        <v>1</v>
+      </c>
+      <c r="G284" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -5280,6 +6988,12 @@
         <v>9</v>
       </c>
       <c r="E285" t="n">
+        <v>0</v>
+      </c>
+      <c r="F285" t="n">
+        <v>0</v>
+      </c>
+      <c r="G285" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -5297,6 +7011,12 @@
         <v>7</v>
       </c>
       <c r="E286" t="n">
+        <v>2</v>
+      </c>
+      <c r="F286" t="n">
+        <v>1</v>
+      </c>
+      <c r="G286" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -5314,6 +7034,12 @@
         <v>7</v>
       </c>
       <c r="E287" t="n">
+        <v>1</v>
+      </c>
+      <c r="F287" t="n">
+        <v>0</v>
+      </c>
+      <c r="G287" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -5331,6 +7057,12 @@
         <v>7</v>
       </c>
       <c r="E288" t="n">
+        <v>3</v>
+      </c>
+      <c r="F288" t="n">
+        <v>1</v>
+      </c>
+      <c r="G288" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -5348,6 +7080,12 @@
         <v>9</v>
       </c>
       <c r="E289" t="n">
+        <v>2</v>
+      </c>
+      <c r="F289" t="n">
+        <v>0</v>
+      </c>
+      <c r="G289" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -5365,6 +7103,12 @@
         <v>7</v>
       </c>
       <c r="E290" t="n">
+        <v>3</v>
+      </c>
+      <c r="F290" t="n">
+        <v>1</v>
+      </c>
+      <c r="G290" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -5382,6 +7126,12 @@
         <v>9</v>
       </c>
       <c r="E291" t="n">
+        <v>5</v>
+      </c>
+      <c r="F291" t="n">
+        <v>1</v>
+      </c>
+      <c r="G291" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -5399,6 +7149,12 @@
         <v>9</v>
       </c>
       <c r="E292" t="n">
+        <v>8</v>
+      </c>
+      <c r="F292" t="n">
+        <v>0</v>
+      </c>
+      <c r="G292" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -5416,6 +7172,12 @@
         <v>7</v>
       </c>
       <c r="E293" t="n">
+        <v>6</v>
+      </c>
+      <c r="F293" t="n">
+        <v>0</v>
+      </c>
+      <c r="G293" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -5433,6 +7195,12 @@
         <v>9</v>
       </c>
       <c r="E294" t="n">
+        <v>5</v>
+      </c>
+      <c r="F294" t="n">
+        <v>0</v>
+      </c>
+      <c r="G294" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -5450,6 +7218,12 @@
         <v>7</v>
       </c>
       <c r="E295" t="n">
+        <v>5</v>
+      </c>
+      <c r="F295" t="n">
+        <v>1</v>
+      </c>
+      <c r="G295" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -5467,6 +7241,12 @@
         <v>7</v>
       </c>
       <c r="E296" t="n">
+        <v>4</v>
+      </c>
+      <c r="F296" t="n">
+        <v>0</v>
+      </c>
+      <c r="G296" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -5484,6 +7264,12 @@
         <v>7</v>
       </c>
       <c r="E297" t="n">
+        <v>1</v>
+      </c>
+      <c r="F297" t="n">
+        <v>0</v>
+      </c>
+      <c r="G297" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -5501,6 +7287,12 @@
         <v>7</v>
       </c>
       <c r="E298" t="n">
+        <v>8</v>
+      </c>
+      <c r="F298" t="n">
+        <v>1</v>
+      </c>
+      <c r="G298" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -5518,6 +7310,12 @@
         <v>9</v>
       </c>
       <c r="E299" t="n">
+        <v>8</v>
+      </c>
+      <c r="F299" t="n">
+        <v>1</v>
+      </c>
+      <c r="G299" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -5535,6 +7333,12 @@
         <v>7</v>
       </c>
       <c r="E300" t="n">
+        <v>4</v>
+      </c>
+      <c r="F300" t="n">
+        <v>1</v>
+      </c>
+      <c r="G300" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -5552,6 +7356,12 @@
         <v>7</v>
       </c>
       <c r="E301" t="n">
+        <v>5</v>
+      </c>
+      <c r="F301" t="n">
+        <v>2</v>
+      </c>
+      <c r="G301" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -5569,6 +7379,12 @@
         <v>9</v>
       </c>
       <c r="E302" t="n">
+        <v>8</v>
+      </c>
+      <c r="F302" t="n">
+        <v>1</v>
+      </c>
+      <c r="G302" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -5586,6 +7402,12 @@
         <v>9</v>
       </c>
       <c r="E303" t="n">
+        <v>11</v>
+      </c>
+      <c r="F303" t="n">
+        <v>2</v>
+      </c>
+      <c r="G303" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -5603,6 +7425,12 @@
         <v>9</v>
       </c>
       <c r="E304" t="n">
+        <v>10</v>
+      </c>
+      <c r="F304" t="n">
+        <v>1</v>
+      </c>
+      <c r="G304" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -5620,6 +7448,12 @@
         <v>7</v>
       </c>
       <c r="E305" t="n">
+        <v>3</v>
+      </c>
+      <c r="F305" t="n">
+        <v>2</v>
+      </c>
+      <c r="G305" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -5637,6 +7471,12 @@
         <v>7</v>
       </c>
       <c r="E306" t="n">
+        <v>4</v>
+      </c>
+      <c r="F306" t="n">
+        <v>1</v>
+      </c>
+      <c r="G306" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -5654,6 +7494,12 @@
         <v>9</v>
       </c>
       <c r="E307" t="n">
+        <v>5</v>
+      </c>
+      <c r="F307" t="n">
+        <v>2</v>
+      </c>
+      <c r="G307" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -5671,6 +7517,12 @@
         <v>7</v>
       </c>
       <c r="E308" t="n">
+        <v>1</v>
+      </c>
+      <c r="F308" t="n">
+        <v>3</v>
+      </c>
+      <c r="G308" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -5688,6 +7540,12 @@
         <v>7</v>
       </c>
       <c r="E309" t="n">
+        <v>0</v>
+      </c>
+      <c r="F309" t="n">
+        <v>1</v>
+      </c>
+      <c r="G309" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -5705,6 +7563,12 @@
         <v>7</v>
       </c>
       <c r="E310" t="n">
+        <v>8</v>
+      </c>
+      <c r="F310" t="n">
+        <v>4</v>
+      </c>
+      <c r="G310" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -5722,6 +7586,12 @@
         <v>9</v>
       </c>
       <c r="E311" t="n">
+        <v>6</v>
+      </c>
+      <c r="F311" t="n">
+        <v>2</v>
+      </c>
+      <c r="G311" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -5739,6 +7609,12 @@
         <v>7</v>
       </c>
       <c r="E312" t="n">
+        <v>3</v>
+      </c>
+      <c r="F312" t="n">
+        <v>0</v>
+      </c>
+      <c r="G312" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -5756,6 +7632,12 @@
         <v>7</v>
       </c>
       <c r="E313" t="n">
+        <v>6</v>
+      </c>
+      <c r="F313" t="n">
+        <v>0</v>
+      </c>
+      <c r="G313" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -5773,6 +7655,12 @@
         <v>9</v>
       </c>
       <c r="E314" t="n">
+        <v>1</v>
+      </c>
+      <c r="F314" t="n">
+        <v>0</v>
+      </c>
+      <c r="G314" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -5790,6 +7678,12 @@
         <v>9</v>
       </c>
       <c r="E315" t="n">
+        <v>4</v>
+      </c>
+      <c r="F315" t="n">
+        <v>0</v>
+      </c>
+      <c r="G315" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -5807,6 +7701,12 @@
         <v>9</v>
       </c>
       <c r="E316" t="n">
+        <v>4</v>
+      </c>
+      <c r="F316" t="n">
+        <v>0</v>
+      </c>
+      <c r="G316" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -5824,6 +7724,12 @@
         <v>7</v>
       </c>
       <c r="E317" t="n">
+        <v>3</v>
+      </c>
+      <c r="F317" t="n">
+        <v>1</v>
+      </c>
+      <c r="G317" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -5841,6 +7747,12 @@
         <v>7</v>
       </c>
       <c r="E318" t="n">
+        <v>2</v>
+      </c>
+      <c r="F318" t="n">
+        <v>2</v>
+      </c>
+      <c r="G318" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -5858,6 +7770,12 @@
         <v>7</v>
       </c>
       <c r="E319" t="n">
+        <v>5</v>
+      </c>
+      <c r="F319" t="n">
+        <v>0</v>
+      </c>
+      <c r="G319" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -5875,6 +7793,12 @@
         <v>9</v>
       </c>
       <c r="E320" t="n">
+        <v>13</v>
+      </c>
+      <c r="F320" t="n">
+        <v>0</v>
+      </c>
+      <c r="G320" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -5892,6 +7816,12 @@
         <v>7</v>
       </c>
       <c r="E321" t="n">
+        <v>2</v>
+      </c>
+      <c r="F321" t="n">
+        <v>2</v>
+      </c>
+      <c r="G321" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -5909,6 +7839,12 @@
         <v>7</v>
       </c>
       <c r="E322" t="n">
+        <v>0</v>
+      </c>
+      <c r="F322" t="n">
+        <v>0</v>
+      </c>
+      <c r="G322" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -5926,6 +7862,12 @@
         <v>9</v>
       </c>
       <c r="E323" t="n">
+        <v>9</v>
+      </c>
+      <c r="F323" t="n">
+        <v>0</v>
+      </c>
+      <c r="G323" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -5943,6 +7885,12 @@
         <v>9</v>
       </c>
       <c r="E324" t="n">
+        <v>0</v>
+      </c>
+      <c r="F324" t="n">
+        <v>0</v>
+      </c>
+      <c r="G324" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -5960,6 +7908,12 @@
         <v>7</v>
       </c>
       <c r="E325" t="n">
+        <v>1</v>
+      </c>
+      <c r="F325" t="n">
+        <v>0</v>
+      </c>
+      <c r="G325" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -5977,6 +7931,12 @@
         <v>9</v>
       </c>
       <c r="E326" t="n">
+        <v>2</v>
+      </c>
+      <c r="F326" t="n">
+        <v>0</v>
+      </c>
+      <c r="G326" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -5994,6 +7954,12 @@
         <v>7</v>
       </c>
       <c r="E327" t="n">
+        <v>3</v>
+      </c>
+      <c r="F327" t="n">
+        <v>1</v>
+      </c>
+      <c r="G327" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -6011,6 +7977,12 @@
         <v>7</v>
       </c>
       <c r="E328" t="n">
+        <v>4</v>
+      </c>
+      <c r="F328" t="n">
+        <v>1</v>
+      </c>
+      <c r="G328" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -6028,6 +8000,12 @@
         <v>9</v>
       </c>
       <c r="E329" t="n">
+        <v>9</v>
+      </c>
+      <c r="F329" t="n">
+        <v>1</v>
+      </c>
+      <c r="G329" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -6045,6 +8023,12 @@
         <v>9</v>
       </c>
       <c r="E330" t="n">
+        <v>3</v>
+      </c>
+      <c r="F330" t="n">
+        <v>0</v>
+      </c>
+      <c r="G330" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -6062,6 +8046,12 @@
         <v>7</v>
       </c>
       <c r="E331" t="n">
+        <v>10</v>
+      </c>
+      <c r="F331" t="n">
+        <v>0</v>
+      </c>
+      <c r="G331" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -6079,6 +8069,12 @@
         <v>9</v>
       </c>
       <c r="E332" t="n">
+        <v>8</v>
+      </c>
+      <c r="F332" t="n">
+        <v>2</v>
+      </c>
+      <c r="G332" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -6096,6 +8092,12 @@
         <v>7</v>
       </c>
       <c r="E333" t="n">
+        <v>3</v>
+      </c>
+      <c r="F333" t="n">
+        <v>1</v>
+      </c>
+      <c r="G333" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -6113,6 +8115,12 @@
         <v>7</v>
       </c>
       <c r="E334" t="n">
+        <v>3</v>
+      </c>
+      <c r="F334" t="n">
+        <v>0</v>
+      </c>
+      <c r="G334" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -6130,6 +8138,12 @@
         <v>7</v>
       </c>
       <c r="E335" t="n">
+        <v>3</v>
+      </c>
+      <c r="F335" t="n">
+        <v>1</v>
+      </c>
+      <c r="G335" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -6147,6 +8161,12 @@
         <v>9</v>
       </c>
       <c r="E336" t="n">
+        <v>1</v>
+      </c>
+      <c r="F336" t="n">
+        <v>0</v>
+      </c>
+      <c r="G336" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -6164,6 +8184,12 @@
         <v>7</v>
       </c>
       <c r="E337" t="n">
+        <v>7</v>
+      </c>
+      <c r="F337" t="n">
+        <v>0</v>
+      </c>
+      <c r="G337" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -6181,6 +8207,12 @@
         <v>7</v>
       </c>
       <c r="E338" t="n">
+        <v>2</v>
+      </c>
+      <c r="F338" t="n">
+        <v>0</v>
+      </c>
+      <c r="G338" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -6198,6 +8230,12 @@
         <v>7</v>
       </c>
       <c r="E339" t="n">
+        <v>7</v>
+      </c>
+      <c r="F339" t="n">
+        <v>0</v>
+      </c>
+      <c r="G339" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -6215,6 +8253,12 @@
         <v>7</v>
       </c>
       <c r="E340" t="n">
+        <v>1</v>
+      </c>
+      <c r="F340" t="n">
+        <v>0</v>
+      </c>
+      <c r="G340" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -6232,6 +8276,12 @@
         <v>7</v>
       </c>
       <c r="E341" t="n">
+        <v>5</v>
+      </c>
+      <c r="F341" t="n">
+        <v>1</v>
+      </c>
+      <c r="G341" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -6249,6 +8299,12 @@
         <v>9</v>
       </c>
       <c r="E342" t="n">
+        <v>9</v>
+      </c>
+      <c r="F342" t="n">
+        <v>1</v>
+      </c>
+      <c r="G342" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -6266,6 +8322,12 @@
         <v>7</v>
       </c>
       <c r="E343" t="n">
+        <v>9</v>
+      </c>
+      <c r="F343" t="n">
+        <v>0</v>
+      </c>
+      <c r="G343" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -6283,6 +8345,12 @@
         <v>9</v>
       </c>
       <c r="E344" t="n">
+        <v>30</v>
+      </c>
+      <c r="F344" t="n">
+        <v>1</v>
+      </c>
+      <c r="G344" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -6300,6 +8368,12 @@
         <v>7</v>
       </c>
       <c r="E345" t="n">
+        <v>5</v>
+      </c>
+      <c r="F345" t="n">
+        <v>0</v>
+      </c>
+      <c r="G345" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -6317,6 +8391,12 @@
         <v>9</v>
       </c>
       <c r="E346" t="n">
+        <v>6</v>
+      </c>
+      <c r="F346" t="n">
+        <v>0</v>
+      </c>
+      <c r="G346" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -6334,6 +8414,12 @@
         <v>9</v>
       </c>
       <c r="E347" t="n">
+        <v>2</v>
+      </c>
+      <c r="F347" t="n">
+        <v>0</v>
+      </c>
+      <c r="G347" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -6351,6 +8437,12 @@
         <v>7</v>
       </c>
       <c r="E348" t="n">
+        <v>4</v>
+      </c>
+      <c r="F348" t="n">
+        <v>2</v>
+      </c>
+      <c r="G348" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -6368,6 +8460,12 @@
         <v>9</v>
       </c>
       <c r="E349" t="n">
+        <v>0</v>
+      </c>
+      <c r="F349" t="n">
+        <v>0</v>
+      </c>
+      <c r="G349" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -6385,6 +8483,12 @@
         <v>7</v>
       </c>
       <c r="E350" t="n">
+        <v>8</v>
+      </c>
+      <c r="F350" t="n">
+        <v>0</v>
+      </c>
+      <c r="G350" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -6402,6 +8506,12 @@
         <v>9</v>
       </c>
       <c r="E351" t="n">
+        <v>2</v>
+      </c>
+      <c r="F351" t="n">
+        <v>0</v>
+      </c>
+      <c r="G351" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -6419,6 +8529,12 @@
         <v>7</v>
       </c>
       <c r="E352" t="n">
+        <v>6</v>
+      </c>
+      <c r="F352" t="n">
+        <v>2</v>
+      </c>
+      <c r="G352" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -6436,6 +8552,12 @@
         <v>9</v>
       </c>
       <c r="E353" t="n">
+        <v>5</v>
+      </c>
+      <c r="F353" t="n">
+        <v>1</v>
+      </c>
+      <c r="G353" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -6453,6 +8575,12 @@
         <v>7</v>
       </c>
       <c r="E354" t="n">
+        <v>1</v>
+      </c>
+      <c r="F354" t="n">
+        <v>0</v>
+      </c>
+      <c r="G354" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -6470,6 +8598,12 @@
         <v>9</v>
       </c>
       <c r="E355" t="n">
+        <v>3</v>
+      </c>
+      <c r="F355" t="n">
+        <v>0</v>
+      </c>
+      <c r="G355" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -6487,6 +8621,12 @@
         <v>7</v>
       </c>
       <c r="E356" t="n">
+        <v>2</v>
+      </c>
+      <c r="F356" t="n">
+        <v>0</v>
+      </c>
+      <c r="G356" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -6504,6 +8644,12 @@
         <v>7</v>
       </c>
       <c r="E357" t="n">
+        <v>8</v>
+      </c>
+      <c r="F357" t="n">
+        <v>4</v>
+      </c>
+      <c r="G357" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -6521,6 +8667,12 @@
         <v>9</v>
       </c>
       <c r="E358" t="n">
+        <v>6</v>
+      </c>
+      <c r="F358" t="n">
+        <v>1</v>
+      </c>
+      <c r="G358" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -6538,6 +8690,12 @@
         <v>7</v>
       </c>
       <c r="E359" t="n">
+        <v>3</v>
+      </c>
+      <c r="F359" t="n">
+        <v>0</v>
+      </c>
+      <c r="G359" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -6555,6 +8713,12 @@
         <v>9</v>
       </c>
       <c r="E360" t="n">
+        <v>5</v>
+      </c>
+      <c r="F360" t="n">
+        <v>1</v>
+      </c>
+      <c r="G360" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -6572,6 +8736,12 @@
         <v>7</v>
       </c>
       <c r="E361" t="n">
+        <v>5</v>
+      </c>
+      <c r="F361" t="n">
+        <v>1</v>
+      </c>
+      <c r="G361" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -6589,6 +8759,12 @@
         <v>9</v>
       </c>
       <c r="E362" t="n">
+        <v>3</v>
+      </c>
+      <c r="F362" t="n">
+        <v>2</v>
+      </c>
+      <c r="G362" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -6606,6 +8782,12 @@
         <v>7</v>
       </c>
       <c r="E363" t="n">
+        <v>3</v>
+      </c>
+      <c r="F363" t="n">
+        <v>0</v>
+      </c>
+      <c r="G363" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -6623,6 +8805,12 @@
         <v>7</v>
       </c>
       <c r="E364" t="n">
+        <v>9</v>
+      </c>
+      <c r="F364" t="n">
+        <v>6</v>
+      </c>
+      <c r="G364" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -6640,6 +8828,12 @@
         <v>7</v>
       </c>
       <c r="E365" t="n">
+        <v>3</v>
+      </c>
+      <c r="F365" t="n">
+        <v>0</v>
+      </c>
+      <c r="G365" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -6657,6 +8851,12 @@
         <v>9</v>
       </c>
       <c r="E366" t="n">
+        <v>4</v>
+      </c>
+      <c r="F366" t="n">
+        <v>0</v>
+      </c>
+      <c r="G366" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -6674,6 +8874,12 @@
         <v>9</v>
       </c>
       <c r="E367" t="n">
+        <v>9</v>
+      </c>
+      <c r="F367" t="n">
+        <v>3</v>
+      </c>
+      <c r="G367" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -6691,6 +8897,12 @@
         <v>7</v>
       </c>
       <c r="E368" t="n">
+        <v>19</v>
+      </c>
+      <c r="F368" t="n">
+        <v>7</v>
+      </c>
+      <c r="G368" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -6708,6 +8920,12 @@
         <v>9</v>
       </c>
       <c r="E369" t="n">
+        <v>13</v>
+      </c>
+      <c r="F369" t="n">
+        <v>2</v>
+      </c>
+      <c r="G369" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -6725,6 +8943,12 @@
         <v>7</v>
       </c>
       <c r="E370" t="n">
+        <v>1</v>
+      </c>
+      <c r="F370" t="n">
+        <v>0</v>
+      </c>
+      <c r="G370" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -6742,6 +8966,12 @@
         <v>9</v>
       </c>
       <c r="E371" t="n">
+        <v>5</v>
+      </c>
+      <c r="F371" t="n">
+        <v>0</v>
+      </c>
+      <c r="G371" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -6759,6 +8989,12 @@
         <v>7</v>
       </c>
       <c r="E372" t="n">
+        <v>4</v>
+      </c>
+      <c r="F372" t="n">
+        <v>5</v>
+      </c>
+      <c r="G372" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -6776,6 +9012,12 @@
         <v>9</v>
       </c>
       <c r="E373" t="n">
+        <v>5</v>
+      </c>
+      <c r="F373" t="n">
+        <v>0</v>
+      </c>
+      <c r="G373" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -6793,6 +9035,12 @@
         <v>7</v>
       </c>
       <c r="E374" t="n">
+        <v>1</v>
+      </c>
+      <c r="F374" t="n">
+        <v>0</v>
+      </c>
+      <c r="G374" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -6810,6 +9058,12 @@
         <v>9</v>
       </c>
       <c r="E375" t="n">
+        <v>14</v>
+      </c>
+      <c r="F375" t="n">
+        <v>1</v>
+      </c>
+      <c r="G375" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -6827,6 +9081,12 @@
         <v>7</v>
       </c>
       <c r="E376" t="n">
+        <v>5</v>
+      </c>
+      <c r="F376" t="n">
+        <v>0</v>
+      </c>
+      <c r="G376" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -6844,6 +9104,12 @@
         <v>7</v>
       </c>
       <c r="E377" t="n">
+        <v>11</v>
+      </c>
+      <c r="F377" t="n">
+        <v>2</v>
+      </c>
+      <c r="G377" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -6861,6 +9127,12 @@
         <v>7</v>
       </c>
       <c r="E378" t="n">
+        <v>1</v>
+      </c>
+      <c r="F378" t="n">
+        <v>1</v>
+      </c>
+      <c r="G378" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -6878,6 +9150,12 @@
         <v>9</v>
       </c>
       <c r="E379" t="n">
+        <v>1</v>
+      </c>
+      <c r="F379" t="n">
+        <v>1</v>
+      </c>
+      <c r="G379" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -6895,6 +9173,12 @@
         <v>9</v>
       </c>
       <c r="E380" t="n">
+        <v>1</v>
+      </c>
+      <c r="F380" t="n">
+        <v>1</v>
+      </c>
+      <c r="G380" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -6912,6 +9196,12 @@
         <v>7</v>
       </c>
       <c r="E381" t="n">
+        <v>7</v>
+      </c>
+      <c r="F381" t="n">
+        <v>1</v>
+      </c>
+      <c r="G381" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -6929,6 +9219,12 @@
         <v>7</v>
       </c>
       <c r="E382" t="n">
+        <v>3</v>
+      </c>
+      <c r="F382" t="n">
+        <v>0</v>
+      </c>
+      <c r="G382" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -6946,6 +9242,12 @@
         <v>7</v>
       </c>
       <c r="E383" t="n">
+        <v>5</v>
+      </c>
+      <c r="F383" t="n">
+        <v>1</v>
+      </c>
+      <c r="G383" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -6963,6 +9265,12 @@
         <v>9</v>
       </c>
       <c r="E384" t="n">
+        <v>14</v>
+      </c>
+      <c r="F384" t="n">
+        <v>6</v>
+      </c>
+      <c r="G384" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -6980,6 +9288,12 @@
         <v>7</v>
       </c>
       <c r="E385" t="n">
+        <v>9</v>
+      </c>
+      <c r="F385" t="n">
+        <v>4</v>
+      </c>
+      <c r="G385" t="n">
         <v>2001</v>
       </c>
     </row>
@@ -6997,6 +9311,12 @@
         <v>9</v>
       </c>
       <c r="E386" t="n">
+        <v>9</v>
+      </c>
+      <c r="F386" t="n">
+        <v>0</v>
+      </c>
+      <c r="G386" t="n">
         <v>2001</v>
       </c>
     </row>

--- a/Excel Files IPEDS/Trimmed/c2001_trimmed_file.xlsx
+++ b/Excel Files IPEDS/Trimmed/c2001_trimmed_file.xlsx
@@ -14,18 +14,18 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
   <si>
-    <t>UNITID</t>
+    <t>unitid</t>
   </si>
   <si>
-    <t>CIPCODE</t>
+    <t>cipcode</t>
   </si>
   <si>
-    <t>CTOTALT</t>
+    <t>ctotalt</t>
   </si>
   <si>
-    <t>AWLEVEL</t>
+    <t>awlevel</t>
   </si>
   <si>
     <t>crace15</t>
@@ -34,7 +34,10 @@
     <t>crace16</t>
   </si>
   <si>
-    <t>Year</t>
+    <t>majornum</t>
+  </si>
+  <si>
+    <t>year</t>
   </si>
 </sst>
 </file>
@@ -392,10 +395,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G386"/>
+  <dimension ref="A1:H386"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -417,8 +420,11 @@
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="2" spans="1:7">
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
       <c r="A2">
         <v>201885</v>
       </c>
@@ -438,10 +444,13 @@
         <v>3</v>
       </c>
       <c r="G2">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H2">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
       <c r="A3">
         <v>201885</v>
       </c>
@@ -461,10 +470,13 @@
         <v>4</v>
       </c>
       <c r="G3">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H3">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
       <c r="A4">
         <v>201645</v>
       </c>
@@ -484,10 +496,13 @@
         <v>2</v>
       </c>
       <c r="G4">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H4">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
       <c r="A5">
         <v>203517</v>
       </c>
@@ -507,10 +522,13 @@
         <v>1</v>
       </c>
       <c r="G5">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H5">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
       <c r="A6">
         <v>203517</v>
       </c>
@@ -530,10 +548,13 @@
         <v>0</v>
       </c>
       <c r="G6">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H6">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
       <c r="A7">
         <v>203368</v>
       </c>
@@ -553,10 +574,13 @@
         <v>2</v>
       </c>
       <c r="G7">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H7">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
       <c r="A8">
         <v>201645</v>
       </c>
@@ -576,10 +600,13 @@
         <v>3</v>
       </c>
       <c r="G8">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H8">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
       <c r="A9">
         <v>204024</v>
       </c>
@@ -599,10 +626,13 @@
         <v>0</v>
       </c>
       <c r="G9">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H9">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
       <c r="A10">
         <v>204796</v>
       </c>
@@ -622,10 +652,13 @@
         <v>5</v>
       </c>
       <c r="G10">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H10">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8">
       <c r="A11">
         <v>201441</v>
       </c>
@@ -645,10 +678,13 @@
         <v>1</v>
       </c>
       <c r="G11">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H11">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8">
       <c r="A12">
         <v>100654</v>
       </c>
@@ -668,10 +704,13 @@
         <v>0</v>
       </c>
       <c r="G12">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H12">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8">
       <c r="A13">
         <v>100663</v>
       </c>
@@ -691,10 +730,13 @@
         <v>0</v>
       </c>
       <c r="G13">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H13">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8">
       <c r="A14">
         <v>100663</v>
       </c>
@@ -714,10 +756,13 @@
         <v>0</v>
       </c>
       <c r="G14">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H14">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8">
       <c r="A15">
         <v>200800</v>
       </c>
@@ -737,10 +782,13 @@
         <v>0</v>
       </c>
       <c r="G15">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H15">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8">
       <c r="A16">
         <v>100706</v>
       </c>
@@ -760,10 +808,13 @@
         <v>2</v>
       </c>
       <c r="G16">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H16">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8">
       <c r="A17">
         <v>100706</v>
       </c>
@@ -783,10 +834,13 @@
         <v>1</v>
       </c>
       <c r="G17">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H17">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8">
       <c r="A18">
         <v>200280</v>
       </c>
@@ -806,10 +860,13 @@
         <v>0</v>
       </c>
       <c r="G18">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H18">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8">
       <c r="A19">
         <v>200332</v>
       </c>
@@ -829,10 +886,13 @@
         <v>0</v>
       </c>
       <c r="G19">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H19">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8">
       <c r="A20">
         <v>200332</v>
       </c>
@@ -852,10 +912,13 @@
         <v>0</v>
       </c>
       <c r="G20">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H20">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8">
       <c r="A21">
         <v>199847</v>
       </c>
@@ -875,10 +938,13 @@
         <v>1</v>
       </c>
       <c r="G21">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H21">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8">
       <c r="A22">
         <v>199193</v>
       </c>
@@ -898,10 +964,13 @@
         <v>1</v>
       </c>
       <c r="G22">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H22">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8">
       <c r="A23">
         <v>199193</v>
       </c>
@@ -921,10 +990,13 @@
         <v>1</v>
       </c>
       <c r="G23">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H23">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8">
       <c r="A24">
         <v>199120</v>
       </c>
@@ -944,10 +1016,13 @@
         <v>3</v>
       </c>
       <c r="G24">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H24">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8">
       <c r="A25">
         <v>199120</v>
       </c>
@@ -967,10 +1042,13 @@
         <v>1</v>
       </c>
       <c r="G25">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H25">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8">
       <c r="A26">
         <v>199139</v>
       </c>
@@ -990,10 +1068,13 @@
         <v>0</v>
       </c>
       <c r="G26">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H26">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8">
       <c r="A27">
         <v>199102</v>
       </c>
@@ -1013,10 +1094,13 @@
         <v>1</v>
       </c>
       <c r="G27">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H27">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8">
       <c r="A28">
         <v>198419</v>
       </c>
@@ -1036,10 +1120,13 @@
         <v>0</v>
       </c>
       <c r="G28">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H28">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8">
       <c r="A29">
         <v>198464</v>
       </c>
@@ -1059,10 +1146,13 @@
         <v>0</v>
       </c>
       <c r="G29">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H29">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8">
       <c r="A30">
         <v>198419</v>
       </c>
@@ -1082,10 +1172,13 @@
         <v>0</v>
       </c>
       <c r="G30">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H30">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8">
       <c r="A31">
         <v>197869</v>
       </c>
@@ -1105,10 +1198,13 @@
         <v>0</v>
       </c>
       <c r="G31">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H31">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8">
       <c r="A32">
         <v>196413</v>
       </c>
@@ -1128,10 +1224,13 @@
         <v>5</v>
       </c>
       <c r="G32">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H32">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8">
       <c r="A33">
         <v>196413</v>
       </c>
@@ -1151,10 +1250,13 @@
         <v>0</v>
       </c>
       <c r="G33">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H33">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8">
       <c r="A34">
         <v>196088</v>
       </c>
@@ -1174,10 +1276,13 @@
         <v>0</v>
       </c>
       <c r="G34">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H34">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8">
       <c r="A35">
         <v>196088</v>
       </c>
@@ -1197,10 +1302,13 @@
         <v>2</v>
       </c>
       <c r="G35">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H35">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8">
       <c r="A36">
         <v>196097</v>
       </c>
@@ -1220,10 +1328,13 @@
         <v>3</v>
       </c>
       <c r="G36">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H36">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8">
       <c r="A37">
         <v>196097</v>
       </c>
@@ -1243,10 +1354,13 @@
         <v>0</v>
       </c>
       <c r="G37">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H37">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8">
       <c r="A38">
         <v>196060</v>
       </c>
@@ -1266,10 +1380,13 @@
         <v>2</v>
       </c>
       <c r="G38">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="39" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H38">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8">
       <c r="A39">
         <v>196060</v>
       </c>
@@ -1289,10 +1406,13 @@
         <v>3</v>
       </c>
       <c r="G39">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="40" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H39">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8">
       <c r="A40">
         <v>196079</v>
       </c>
@@ -1312,10 +1432,13 @@
         <v>0</v>
       </c>
       <c r="G40">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="41" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H40">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8">
       <c r="A41">
         <v>195030</v>
       </c>
@@ -1335,10 +1458,13 @@
         <v>2</v>
       </c>
       <c r="G41">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="42" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H41">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8">
       <c r="A42">
         <v>194541</v>
       </c>
@@ -1358,10 +1484,13 @@
         <v>0</v>
       </c>
       <c r="G42">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="43" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H42">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8">
       <c r="A43">
         <v>194824</v>
       </c>
@@ -1381,10 +1510,13 @@
         <v>2</v>
       </c>
       <c r="G43">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="44" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H43">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8">
       <c r="A44">
         <v>194824</v>
       </c>
@@ -1404,10 +1536,13 @@
         <v>1</v>
       </c>
       <c r="G44">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="45" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H44">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8">
       <c r="A45">
         <v>195030</v>
       </c>
@@ -1427,10 +1562,13 @@
         <v>6</v>
       </c>
       <c r="G45">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="46" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H45">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8">
       <c r="A46">
         <v>194541</v>
       </c>
@@ -1450,10 +1588,13 @@
         <v>0</v>
       </c>
       <c r="G46">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="47" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H46">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8">
       <c r="A47">
         <v>193900</v>
       </c>
@@ -1473,10 +1614,13 @@
         <v>3</v>
       </c>
       <c r="G47">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="48" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H47">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8">
       <c r="A48">
         <v>193900</v>
       </c>
@@ -1496,10 +1640,13 @@
         <v>0</v>
       </c>
       <c r="G48">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="49" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H48">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8">
       <c r="A49">
         <v>190594</v>
       </c>
@@ -1519,10 +1666,13 @@
         <v>1</v>
       </c>
       <c r="G49">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="50" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H49">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8">
       <c r="A50">
         <v>190664</v>
       </c>
@@ -1542,10 +1692,13 @@
         <v>0</v>
       </c>
       <c r="G50">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="51" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H50">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8">
       <c r="A51">
         <v>190576</v>
       </c>
@@ -1565,10 +1718,13 @@
         <v>0</v>
       </c>
       <c r="G51">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="52" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H51">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8">
       <c r="A52">
         <v>190150</v>
       </c>
@@ -1588,10 +1744,13 @@
         <v>0</v>
       </c>
       <c r="G52">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="53" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H52">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8">
       <c r="A53">
         <v>190415</v>
       </c>
@@ -1611,10 +1770,13 @@
         <v>6</v>
       </c>
       <c r="G53">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="54" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H53">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8">
       <c r="A54">
         <v>190415</v>
       </c>
@@ -1634,10 +1796,13 @@
         <v>4</v>
       </c>
       <c r="G54">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="55" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H54">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8">
       <c r="A55">
         <v>190044</v>
       </c>
@@ -1657,10 +1822,13 @@
         <v>0</v>
       </c>
       <c r="G55">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="56" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H55">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8">
       <c r="A56">
         <v>190044</v>
       </c>
@@ -1680,10 +1848,13 @@
         <v>0</v>
       </c>
       <c r="G56">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="57" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H56">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8">
       <c r="A57">
         <v>190150</v>
       </c>
@@ -1703,10 +1874,13 @@
         <v>3</v>
       </c>
       <c r="G57">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="58" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H57">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8">
       <c r="A58">
         <v>188429</v>
       </c>
@@ -1726,10 +1900,13 @@
         <v>0</v>
       </c>
       <c r="G58">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="59" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H58">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8">
       <c r="A59">
         <v>188030</v>
       </c>
@@ -1749,10 +1926,13 @@
         <v>0</v>
       </c>
       <c r="G59">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="60" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H59">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8">
       <c r="A60">
         <v>188030</v>
       </c>
@@ -1772,10 +1952,13 @@
         <v>0</v>
       </c>
       <c r="G60">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="61" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H60">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8">
       <c r="A61">
         <v>187967</v>
       </c>
@@ -1795,10 +1978,13 @@
         <v>2</v>
       </c>
       <c r="G61">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="62" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H61">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8">
       <c r="A62">
         <v>187967</v>
       </c>
@@ -1818,10 +2004,13 @@
         <v>0</v>
       </c>
       <c r="G62">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="63" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H62">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8">
       <c r="A63">
         <v>187985</v>
       </c>
@@ -1841,10 +2030,13 @@
         <v>3</v>
       </c>
       <c r="G63">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="64" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H63">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8">
       <c r="A64">
         <v>187985</v>
       </c>
@@ -1864,10 +2056,13 @@
         <v>0</v>
       </c>
       <c r="G64">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="65" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H64">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8">
       <c r="A65">
         <v>186867</v>
       </c>
@@ -1887,10 +2082,13 @@
         <v>1</v>
       </c>
       <c r="G65">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="66" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H65">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8">
       <c r="A66">
         <v>186867</v>
       </c>
@@ -1910,10 +2108,13 @@
         <v>1</v>
       </c>
       <c r="G66">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="67" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H66">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8">
       <c r="A67">
         <v>186131</v>
       </c>
@@ -1933,10 +2134,13 @@
         <v>2</v>
       </c>
       <c r="G67">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="68" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H67">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8">
       <c r="A68">
         <v>186131</v>
       </c>
@@ -1956,10 +2160,13 @@
         <v>4</v>
       </c>
       <c r="G68">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="69" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H68">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8">
       <c r="A69">
         <v>186380</v>
       </c>
@@ -1979,10 +2186,13 @@
         <v>1</v>
       </c>
       <c r="G69">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="70" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H69">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8">
       <c r="A70">
         <v>186380</v>
       </c>
@@ -2002,10 +2212,13 @@
         <v>1</v>
       </c>
       <c r="G70">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="71" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H70">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="71" spans="1:8">
       <c r="A71">
         <v>183044</v>
       </c>
@@ -2025,10 +2238,13 @@
         <v>2</v>
       </c>
       <c r="G71">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="72" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H71">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="72" spans="1:8">
       <c r="A72">
         <v>182670</v>
       </c>
@@ -2048,10 +2264,13 @@
         <v>1</v>
       </c>
       <c r="G72">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="73" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H72">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="73" spans="1:8">
       <c r="A73">
         <v>182670</v>
       </c>
@@ -2071,10 +2290,13 @@
         <v>2</v>
       </c>
       <c r="G73">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="74" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H73">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="74" spans="1:8">
       <c r="A74">
         <v>183044</v>
       </c>
@@ -2094,10 +2316,13 @@
         <v>1</v>
       </c>
       <c r="G74">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="75" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H74">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="75" spans="1:8">
       <c r="A75">
         <v>182281</v>
       </c>
@@ -2117,10 +2342,13 @@
         <v>0</v>
       </c>
       <c r="G75">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="76" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H75">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="76" spans="1:8">
       <c r="A76">
         <v>182281</v>
       </c>
@@ -2140,10 +2368,13 @@
         <v>0</v>
       </c>
       <c r="G76">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="77" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H76">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="77" spans="1:8">
       <c r="A77">
         <v>182290</v>
       </c>
@@ -2163,10 +2394,13 @@
         <v>1</v>
       </c>
       <c r="G77">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="78" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H77">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="78" spans="1:8">
       <c r="A78">
         <v>182290</v>
       </c>
@@ -2186,10 +2420,13 @@
         <v>0</v>
       </c>
       <c r="G78">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="79" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H78">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="79" spans="1:8">
       <c r="A79">
         <v>181464</v>
       </c>
@@ -2209,10 +2446,13 @@
         <v>3</v>
       </c>
       <c r="G79">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="80" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H79">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="80" spans="1:8">
       <c r="A80">
         <v>181464</v>
       </c>
@@ -2232,10 +2472,13 @@
         <v>1</v>
       </c>
       <c r="G80">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="81" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H80">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="81" spans="1:8">
       <c r="A81">
         <v>181002</v>
       </c>
@@ -2255,10 +2498,13 @@
         <v>0</v>
       </c>
       <c r="G81">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="82" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H81">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="82" spans="1:8">
       <c r="A82">
         <v>180461</v>
       </c>
@@ -2278,10 +2524,13 @@
         <v>4</v>
       </c>
       <c r="G82">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="83" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H82">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="83" spans="1:8">
       <c r="A83">
         <v>180461</v>
       </c>
@@ -2301,10 +2550,13 @@
         <v>1</v>
       </c>
       <c r="G83">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="84" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H83">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="84" spans="1:8">
       <c r="A84">
         <v>180489</v>
       </c>
@@ -2324,10 +2576,13 @@
         <v>0</v>
       </c>
       <c r="G84">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="85" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H84">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="85" spans="1:8">
       <c r="A85">
         <v>179867</v>
       </c>
@@ -2347,10 +2602,13 @@
         <v>1</v>
       </c>
       <c r="G85">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="86" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H85">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="86" spans="1:8">
       <c r="A86">
         <v>179867</v>
       </c>
@@ -2370,10 +2628,13 @@
         <v>2</v>
       </c>
       <c r="G86">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="87" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H86">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="87" spans="1:8">
       <c r="A87">
         <v>178402</v>
       </c>
@@ -2393,10 +2654,13 @@
         <v>0</v>
       </c>
       <c r="G87">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="88" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H87">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="88" spans="1:8">
       <c r="A88">
         <v>178411</v>
       </c>
@@ -2416,10 +2680,13 @@
         <v>1</v>
       </c>
       <c r="G88">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="89" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H88">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="89" spans="1:8">
       <c r="A89">
         <v>178420</v>
       </c>
@@ -2439,10 +2706,13 @@
         <v>1</v>
       </c>
       <c r="G89">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="90" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H89">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="90" spans="1:8">
       <c r="A90">
         <v>178420</v>
       </c>
@@ -2462,10 +2732,13 @@
         <v>0</v>
       </c>
       <c r="G90">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="91" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H90">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="91" spans="1:8">
       <c r="A91">
         <v>178396</v>
       </c>
@@ -2485,10 +2758,13 @@
         <v>0</v>
       </c>
       <c r="G91">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="92" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H91">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="92" spans="1:8">
       <c r="A92">
         <v>178396</v>
       </c>
@@ -2508,10 +2784,13 @@
         <v>1</v>
       </c>
       <c r="G92">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="93" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H92">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="93" spans="1:8">
       <c r="A93">
         <v>176372</v>
       </c>
@@ -2531,10 +2810,13 @@
         <v>0</v>
       </c>
       <c r="G93">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="94" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H93">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="94" spans="1:8">
       <c r="A94">
         <v>176080</v>
       </c>
@@ -2554,10 +2836,13 @@
         <v>0</v>
       </c>
       <c r="G94">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="95" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H94">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="95" spans="1:8">
       <c r="A95">
         <v>176017</v>
       </c>
@@ -2577,10 +2862,13 @@
         <v>2</v>
       </c>
       <c r="G95">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="96" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H95">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="96" spans="1:8">
       <c r="A96">
         <v>176017</v>
       </c>
@@ -2600,10 +2888,13 @@
         <v>0</v>
       </c>
       <c r="G96">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="97" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H96">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="97" spans="1:8">
       <c r="A97">
         <v>174233</v>
       </c>
@@ -2623,10 +2914,13 @@
         <v>1</v>
       </c>
       <c r="G97">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="98" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H97">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="98" spans="1:8">
       <c r="A98">
         <v>174066</v>
       </c>
@@ -2646,10 +2940,13 @@
         <v>2</v>
       </c>
       <c r="G98">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="99" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H98">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="99" spans="1:8">
       <c r="A99">
         <v>174066</v>
       </c>
@@ -2669,10 +2966,13 @@
         <v>1</v>
       </c>
       <c r="G99">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="100" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H99">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="100" spans="1:8">
       <c r="A100">
         <v>173920</v>
       </c>
@@ -2692,10 +2992,13 @@
         <v>1</v>
       </c>
       <c r="G100">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="101" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H100">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="101" spans="1:8">
       <c r="A101">
         <v>172699</v>
       </c>
@@ -2715,10 +3018,13 @@
         <v>0</v>
       </c>
       <c r="G101">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="102" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H101">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="102" spans="1:8">
       <c r="A102">
         <v>172699</v>
       </c>
@@ -2738,10 +3044,13 @@
         <v>1</v>
       </c>
       <c r="G102">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="103" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H102">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="103" spans="1:8">
       <c r="A103">
         <v>172644</v>
       </c>
@@ -2761,10 +3070,13 @@
         <v>1</v>
       </c>
       <c r="G103">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="104" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H103">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="104" spans="1:8">
       <c r="A104">
         <v>172644</v>
       </c>
@@ -2784,10 +3096,13 @@
         <v>2</v>
       </c>
       <c r="G104">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="105" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H104">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="105" spans="1:8">
       <c r="A105">
         <v>171571</v>
       </c>
@@ -2807,10 +3122,13 @@
         <v>0</v>
       </c>
       <c r="G105">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="106" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H105">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="106" spans="1:8">
       <c r="A106">
         <v>170976</v>
       </c>
@@ -2830,10 +3148,13 @@
         <v>0</v>
       </c>
       <c r="G106">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="107" spans="1:7">
+        <v>2</v>
+      </c>
+      <c r="H106">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="107" spans="1:8">
       <c r="A107">
         <v>170976</v>
       </c>
@@ -2853,10 +3174,13 @@
         <v>1</v>
       </c>
       <c r="G107">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="108" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H107">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="108" spans="1:8">
       <c r="A108">
         <v>171100</v>
       </c>
@@ -2876,10 +3200,13 @@
         <v>4</v>
       </c>
       <c r="G108">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="109" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H108">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="109" spans="1:8">
       <c r="A109">
         <v>171100</v>
       </c>
@@ -2899,10 +3226,13 @@
         <v>2</v>
       </c>
       <c r="G109">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="110" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H109">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="110" spans="1:8">
       <c r="A110">
         <v>171128</v>
       </c>
@@ -2922,10 +3252,13 @@
         <v>1</v>
       </c>
       <c r="G110">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="111" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H110">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="111" spans="1:8">
       <c r="A111">
         <v>171128</v>
       </c>
@@ -2945,10 +3278,13 @@
         <v>0</v>
       </c>
       <c r="G111">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="112" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H111">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="112" spans="1:8">
       <c r="A112">
         <v>170976</v>
       </c>
@@ -2968,10 +3304,13 @@
         <v>3</v>
       </c>
       <c r="G112">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="113" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H112">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="113" spans="1:8">
       <c r="A113">
         <v>169798</v>
       </c>
@@ -2991,10 +3330,13 @@
         <v>0</v>
       </c>
       <c r="G113">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="114" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H113">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="114" spans="1:8">
       <c r="A114">
         <v>169248</v>
       </c>
@@ -3014,10 +3356,13 @@
         <v>1</v>
       </c>
       <c r="G114">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="115" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H114">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="115" spans="1:8">
       <c r="A115">
         <v>168421</v>
       </c>
@@ -3037,10 +3382,13 @@
         <v>0</v>
       </c>
       <c r="G115">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="116" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H115">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="116" spans="1:8">
       <c r="A116">
         <v>168421</v>
       </c>
@@ -3060,10 +3408,13 @@
         <v>0</v>
       </c>
       <c r="G116">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="117" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H116">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="117" spans="1:8">
       <c r="A117">
         <v>167987</v>
       </c>
@@ -3083,10 +3434,13 @@
         <v>2</v>
       </c>
       <c r="G117">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="118" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H117">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="118" spans="1:8">
       <c r="A118">
         <v>168148</v>
       </c>
@@ -3106,10 +3460,13 @@
         <v>0</v>
       </c>
       <c r="G118">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="119" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H118">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="119" spans="1:8">
       <c r="A119">
         <v>168148</v>
       </c>
@@ -3129,10 +3486,13 @@
         <v>0</v>
       </c>
       <c r="G119">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="120" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H119">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="120" spans="1:8">
       <c r="A120">
         <v>167358</v>
       </c>
@@ -3152,10 +3512,13 @@
         <v>1</v>
       </c>
       <c r="G120">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="121" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H120">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="121" spans="1:8">
       <c r="A121">
         <v>167358</v>
       </c>
@@ -3175,10 +3538,13 @@
         <v>0</v>
       </c>
       <c r="G121">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="122" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H121">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="122" spans="1:8">
       <c r="A122">
         <v>166683</v>
       </c>
@@ -3198,10 +3564,13 @@
         <v>1</v>
       </c>
       <c r="G122">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="123" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H122">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="123" spans="1:8">
       <c r="A123">
         <v>166683</v>
       </c>
@@ -3221,10 +3590,13 @@
         <v>3</v>
       </c>
       <c r="G123">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="124" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H123">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="124" spans="1:8">
       <c r="A124">
         <v>166513</v>
       </c>
@@ -3244,10 +3616,13 @@
         <v>1</v>
       </c>
       <c r="G124">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="125" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H124">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="125" spans="1:8">
       <c r="A125">
         <v>166513</v>
       </c>
@@ -3267,10 +3642,13 @@
         <v>1</v>
       </c>
       <c r="G125">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="126" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H125">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="126" spans="1:8">
       <c r="A126">
         <v>166629</v>
       </c>
@@ -3290,10 +3668,13 @@
         <v>1</v>
       </c>
       <c r="G126">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="127" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H126">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="127" spans="1:8">
       <c r="A127">
         <v>166629</v>
       </c>
@@ -3313,10 +3694,13 @@
         <v>1</v>
       </c>
       <c r="G127">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="128" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H127">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="128" spans="1:8">
       <c r="A128">
         <v>166027</v>
       </c>
@@ -3336,10 +3720,13 @@
         <v>6</v>
       </c>
       <c r="G128">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="129" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H128">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="129" spans="1:8">
       <c r="A129">
         <v>166027</v>
       </c>
@@ -3359,10 +3746,13 @@
         <v>4</v>
       </c>
       <c r="G129">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="130" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H129">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="130" spans="1:8">
       <c r="A130">
         <v>165015</v>
       </c>
@@ -3382,10 +3772,13 @@
         <v>2</v>
       </c>
       <c r="G130">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="131" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H130">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="131" spans="1:8">
       <c r="A131">
         <v>165015</v>
       </c>
@@ -3405,10 +3798,13 @@
         <v>2</v>
       </c>
       <c r="G131">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="132" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H131">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="132" spans="1:8">
       <c r="A132">
         <v>165334</v>
       </c>
@@ -3428,10 +3824,13 @@
         <v>0</v>
       </c>
       <c r="G132">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="133" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H132">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="133" spans="1:8">
       <c r="A133">
         <v>165334</v>
       </c>
@@ -3451,10 +3850,13 @@
         <v>0</v>
       </c>
       <c r="G133">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="134" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H133">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="134" spans="1:8">
       <c r="A134">
         <v>164924</v>
       </c>
@@ -3474,10 +3876,13 @@
         <v>0</v>
       </c>
       <c r="G134">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="135" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H134">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="135" spans="1:8">
       <c r="A135">
         <v>164924</v>
       </c>
@@ -3497,10 +3902,13 @@
         <v>2</v>
       </c>
       <c r="G135">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="136" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H135">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="136" spans="1:8">
       <c r="A136">
         <v>164988</v>
       </c>
@@ -3520,10 +3928,13 @@
         <v>2</v>
       </c>
       <c r="G136">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="137" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H136">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="137" spans="1:8">
       <c r="A137">
         <v>164988</v>
       </c>
@@ -3543,10 +3954,13 @@
         <v>1</v>
       </c>
       <c r="G137">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="138" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H137">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="138" spans="1:8">
       <c r="A138">
         <v>163268</v>
       </c>
@@ -3566,10 +3980,13 @@
         <v>0</v>
       </c>
       <c r="G138">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="139" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H138">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="139" spans="1:8">
       <c r="A139">
         <v>163286</v>
       </c>
@@ -3589,10 +4006,13 @@
         <v>6</v>
       </c>
       <c r="G139">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="140" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H139">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="140" spans="1:8">
       <c r="A140">
         <v>163286</v>
       </c>
@@ -3612,10 +4032,13 @@
         <v>1</v>
       </c>
       <c r="G140">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="141" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H140">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="141" spans="1:8">
       <c r="A141">
         <v>162928</v>
       </c>
@@ -3635,10 +4058,13 @@
         <v>7</v>
       </c>
       <c r="G141">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="142" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H141">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="142" spans="1:8">
       <c r="A142">
         <v>162928</v>
       </c>
@@ -3658,10 +4084,13 @@
         <v>1</v>
       </c>
       <c r="G142">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="143" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H142">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="143" spans="1:8">
       <c r="A143">
         <v>163268</v>
       </c>
@@ -3681,10 +4110,13 @@
         <v>1</v>
       </c>
       <c r="G143">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="144" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H143">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="144" spans="1:8">
       <c r="A144">
         <v>161253</v>
       </c>
@@ -3704,10 +4136,13 @@
         <v>0</v>
       </c>
       <c r="G144">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="145" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H144">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="145" spans="1:8">
       <c r="A145">
         <v>160755</v>
       </c>
@@ -3727,10 +4162,13 @@
         <v>0</v>
       </c>
       <c r="G145">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="146" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H145">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="146" spans="1:8">
       <c r="A146">
         <v>160755</v>
       </c>
@@ -3750,10 +4188,13 @@
         <v>1</v>
       </c>
       <c r="G146">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="147" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H146">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="147" spans="1:8">
       <c r="A147">
         <v>160621</v>
       </c>
@@ -3773,10 +4214,13 @@
         <v>1</v>
       </c>
       <c r="G147">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="148" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H147">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="148" spans="1:8">
       <c r="A148">
         <v>160658</v>
       </c>
@@ -3796,10 +4240,13 @@
         <v>0</v>
       </c>
       <c r="G148">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="149" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H148">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="149" spans="1:8">
       <c r="A149">
         <v>159647</v>
       </c>
@@ -3819,10 +4266,13 @@
         <v>0</v>
       </c>
       <c r="G149">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="150" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H149">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="150" spans="1:8">
       <c r="A150">
         <v>159939</v>
       </c>
@@ -3842,10 +4292,13 @@
         <v>2</v>
       </c>
       <c r="G150">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="151" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H150">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="151" spans="1:8">
       <c r="A151">
         <v>159391</v>
       </c>
@@ -3865,10 +4318,13 @@
         <v>1</v>
       </c>
       <c r="G151">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="152" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H151">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="152" spans="1:8">
       <c r="A152">
         <v>159391</v>
       </c>
@@ -3888,10 +4344,13 @@
         <v>1</v>
       </c>
       <c r="G152">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="153" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H152">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="153" spans="1:8">
       <c r="A153">
         <v>157085</v>
       </c>
@@ -3911,10 +4370,13 @@
         <v>3</v>
       </c>
       <c r="G153">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="154" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H153">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="154" spans="1:8">
       <c r="A154">
         <v>157289</v>
       </c>
@@ -3934,10 +4396,13 @@
         <v>0</v>
       </c>
       <c r="G154">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="155" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H154">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="155" spans="1:8">
       <c r="A155">
         <v>157085</v>
       </c>
@@ -3957,10 +4422,13 @@
         <v>2</v>
       </c>
       <c r="G155">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="156" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H155">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="156" spans="1:8">
       <c r="A156">
         <v>156620</v>
       </c>
@@ -3980,10 +4448,13 @@
         <v>0</v>
       </c>
       <c r="G156">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="157" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H156">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="157" spans="1:8">
       <c r="A157">
         <v>156125</v>
       </c>
@@ -4003,10 +4474,13 @@
         <v>1</v>
       </c>
       <c r="G157">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="158" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H157">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="158" spans="1:8">
       <c r="A158">
         <v>155317</v>
       </c>
@@ -4026,10 +4500,13 @@
         <v>1</v>
       </c>
       <c r="G158">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="159" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H158">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="159" spans="1:8">
       <c r="A159">
         <v>155399</v>
       </c>
@@ -4049,10 +4526,13 @@
         <v>0</v>
       </c>
       <c r="G159">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="160" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H159">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="160" spans="1:8">
       <c r="A160">
         <v>155399</v>
       </c>
@@ -4072,10 +4552,13 @@
         <v>1</v>
       </c>
       <c r="G160">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="161" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H160">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="161" spans="1:8">
       <c r="A161">
         <v>155317</v>
       </c>
@@ -4095,10 +4578,13 @@
         <v>1</v>
       </c>
       <c r="G161">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="162" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H161">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="162" spans="1:8">
       <c r="A162">
         <v>153658</v>
       </c>
@@ -4118,10 +4604,13 @@
         <v>0</v>
       </c>
       <c r="G162">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="163" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H162">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="163" spans="1:8">
       <c r="A163">
         <v>153658</v>
       </c>
@@ -4141,10 +4630,13 @@
         <v>0</v>
       </c>
       <c r="G163">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="164" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H163">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="164" spans="1:8">
       <c r="A164">
         <v>153603</v>
       </c>
@@ -4164,10 +4656,13 @@
         <v>0</v>
       </c>
       <c r="G164">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="165" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H164">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="165" spans="1:8">
       <c r="A165">
         <v>153603</v>
       </c>
@@ -4187,10 +4682,13 @@
         <v>0</v>
       </c>
       <c r="G165">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="166" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H165">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="166" spans="1:8">
       <c r="A166">
         <v>152080</v>
       </c>
@@ -4210,10 +4708,13 @@
         <v>0</v>
       </c>
       <c r="G166">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="167" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H166">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="167" spans="1:8">
       <c r="A167">
         <v>152080</v>
       </c>
@@ -4233,10 +4734,13 @@
         <v>3</v>
       </c>
       <c r="G167">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="168" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H167">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="168" spans="1:8">
       <c r="A168">
         <v>151351</v>
       </c>
@@ -4256,10 +4760,13 @@
         <v>2</v>
       </c>
       <c r="G168">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="169" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H168">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="169" spans="1:8">
       <c r="A169">
         <v>151351</v>
       </c>
@@ -4279,10 +4786,13 @@
         <v>1</v>
       </c>
       <c r="G169">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="170" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H169">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="170" spans="1:8">
       <c r="A170">
         <v>151324</v>
       </c>
@@ -4302,10 +4812,13 @@
         <v>1</v>
       </c>
       <c r="G170">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="171" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H170">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="171" spans="1:8">
       <c r="A171">
         <v>151111</v>
       </c>
@@ -4325,10 +4838,13 @@
         <v>0</v>
       </c>
       <c r="G171">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="172" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H171">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="172" spans="1:8">
       <c r="A172">
         <v>151111</v>
       </c>
@@ -4348,10 +4864,13 @@
         <v>0</v>
       </c>
       <c r="G172">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="173" spans="1:7">
+        <v>2</v>
+      </c>
+      <c r="H172">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="173" spans="1:8">
       <c r="A173">
         <v>149772</v>
       </c>
@@ -4371,10 +4890,13 @@
         <v>2</v>
       </c>
       <c r="G173">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="174" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H173">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="174" spans="1:8">
       <c r="A174">
         <v>150136</v>
       </c>
@@ -4394,10 +4916,13 @@
         <v>1</v>
       </c>
       <c r="G174">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="175" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H174">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="175" spans="1:8">
       <c r="A175">
         <v>149231</v>
       </c>
@@ -4417,10 +4942,13 @@
         <v>0</v>
       </c>
       <c r="G175">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="176" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H175">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="176" spans="1:8">
       <c r="A176">
         <v>149222</v>
       </c>
@@ -4440,10 +4968,13 @@
         <v>1</v>
       </c>
       <c r="G176">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="177" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H176">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="177" spans="1:8">
       <c r="A177">
         <v>147776</v>
       </c>
@@ -4463,10 +4994,13 @@
         <v>1</v>
       </c>
       <c r="G177">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="178" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H177">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="178" spans="1:8">
       <c r="A178">
         <v>147703</v>
       </c>
@@ -4486,10 +5020,13 @@
         <v>2</v>
       </c>
       <c r="G178">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="179" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H178">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="179" spans="1:8">
       <c r="A179">
         <v>147703</v>
       </c>
@@ -4509,10 +5046,13 @@
         <v>0</v>
       </c>
       <c r="G179">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="180" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H179">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="180" spans="1:8">
       <c r="A180">
         <v>147767</v>
       </c>
@@ -4532,10 +5072,13 @@
         <v>0</v>
       </c>
       <c r="G180">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="181" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H180">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="181" spans="1:8">
       <c r="A181">
         <v>147767</v>
       </c>
@@ -4555,10 +5098,13 @@
         <v>1</v>
       </c>
       <c r="G181">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="182" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H181">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="182" spans="1:8">
       <c r="A182">
         <v>145725</v>
       </c>
@@ -4578,10 +5124,13 @@
         <v>0</v>
       </c>
       <c r="G182">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="183" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H182">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="183" spans="1:8">
       <c r="A183">
         <v>145637</v>
       </c>
@@ -4601,10 +5150,13 @@
         <v>5</v>
       </c>
       <c r="G183">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="184" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H183">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="184" spans="1:8">
       <c r="A184">
         <v>145637</v>
       </c>
@@ -4624,10 +5176,13 @@
         <v>2</v>
       </c>
       <c r="G184">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="185" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H184">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="185" spans="1:8">
       <c r="A185">
         <v>145600</v>
       </c>
@@ -4647,10 +5202,13 @@
         <v>5</v>
       </c>
       <c r="G185">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="186" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H185">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="186" spans="1:8">
       <c r="A186">
         <v>145600</v>
       </c>
@@ -4670,10 +5228,13 @@
         <v>0</v>
       </c>
       <c r="G186">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="187" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H186">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="187" spans="1:8">
       <c r="A187">
         <v>144740</v>
       </c>
@@ -4693,10 +5254,13 @@
         <v>0</v>
       </c>
       <c r="G187">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="188" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H187">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="188" spans="1:8">
       <c r="A188">
         <v>144050</v>
       </c>
@@ -4716,10 +5280,13 @@
         <v>0</v>
       </c>
       <c r="G188">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="189" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H188">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="189" spans="1:8">
       <c r="A189">
         <v>144050</v>
       </c>
@@ -4739,10 +5306,13 @@
         <v>1</v>
       </c>
       <c r="G189">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="190" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H189">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="190" spans="1:8">
       <c r="A190">
         <v>142285</v>
       </c>
@@ -4762,10 +5332,13 @@
         <v>0</v>
       </c>
       <c r="G190">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="191" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H190">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="191" spans="1:8">
       <c r="A191">
         <v>142276</v>
       </c>
@@ -4785,10 +5358,13 @@
         <v>0</v>
       </c>
       <c r="G191">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="192" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H191">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="192" spans="1:8">
       <c r="A192">
         <v>141574</v>
       </c>
@@ -4808,10 +5384,13 @@
         <v>0</v>
       </c>
       <c r="G192">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="193" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H192">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="193" spans="1:8">
       <c r="A193">
         <v>141574</v>
       </c>
@@ -4831,10 +5410,13 @@
         <v>0</v>
       </c>
       <c r="G193">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="194" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H193">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="194" spans="1:8">
       <c r="A194">
         <v>139959</v>
       </c>
@@ -4854,10 +5436,13 @@
         <v>0</v>
       </c>
       <c r="G194">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="195" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H194">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="195" spans="1:8">
       <c r="A195">
         <v>139959</v>
       </c>
@@ -4877,10 +5462,13 @@
         <v>1</v>
       </c>
       <c r="G195">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="196" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H195">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="196" spans="1:8">
       <c r="A196">
         <v>139940</v>
       </c>
@@ -4900,10 +5488,13 @@
         <v>0</v>
       </c>
       <c r="G196">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="197" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H196">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="197" spans="1:8">
       <c r="A197">
         <v>139755</v>
       </c>
@@ -4923,10 +5514,13 @@
         <v>0</v>
       </c>
       <c r="G197">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="198" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H197">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="198" spans="1:8">
       <c r="A198">
         <v>139755</v>
       </c>
@@ -4946,10 +5540,13 @@
         <v>1</v>
       </c>
       <c r="G198">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="199" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H198">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="199" spans="1:8">
       <c r="A199">
         <v>138947</v>
       </c>
@@ -4969,10 +5566,13 @@
         <v>1</v>
       </c>
       <c r="G199">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="200" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H199">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="200" spans="1:8">
       <c r="A200">
         <v>137351</v>
       </c>
@@ -4992,10 +5592,13 @@
         <v>0</v>
       </c>
       <c r="G200">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="201" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H200">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="201" spans="1:8">
       <c r="A201">
         <v>135726</v>
       </c>
@@ -5015,10 +5618,13 @@
         <v>0</v>
       </c>
       <c r="G201">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="202" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H201">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="202" spans="1:8">
       <c r="A202">
         <v>135726</v>
       </c>
@@ -5038,10 +5644,13 @@
         <v>0</v>
       </c>
       <c r="G202">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="203" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H202">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="203" spans="1:8">
       <c r="A203">
         <v>134130</v>
       </c>
@@ -5061,10 +5670,13 @@
         <v>1</v>
       </c>
       <c r="G203">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="204" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H203">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="204" spans="1:8">
       <c r="A204">
         <v>134130</v>
       </c>
@@ -5084,10 +5696,13 @@
         <v>1</v>
       </c>
       <c r="G204">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="205" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H204">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="205" spans="1:8">
       <c r="A205">
         <v>133951</v>
       </c>
@@ -5107,10 +5722,13 @@
         <v>3</v>
       </c>
       <c r="G205">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="206" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H205">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="206" spans="1:8">
       <c r="A206">
         <v>134097</v>
       </c>
@@ -5130,10 +5748,13 @@
         <v>1</v>
       </c>
       <c r="G206">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="207" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H206">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="207" spans="1:8">
       <c r="A207">
         <v>134097</v>
       </c>
@@ -5153,10 +5774,13 @@
         <v>3</v>
       </c>
       <c r="G207">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="208" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H207">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="208" spans="1:8">
       <c r="A208">
         <v>133669</v>
       </c>
@@ -5176,10 +5800,13 @@
         <v>0</v>
       </c>
       <c r="G208">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="209" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H208">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="209" spans="1:8">
       <c r="A209">
         <v>133669</v>
       </c>
@@ -5199,10 +5826,13 @@
         <v>0</v>
       </c>
       <c r="G209">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="210" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H209">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="210" spans="1:8">
       <c r="A210">
         <v>132903</v>
       </c>
@@ -5222,10 +5852,13 @@
         <v>2</v>
       </c>
       <c r="G210">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="211" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H210">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="211" spans="1:8">
       <c r="A211">
         <v>132903</v>
       </c>
@@ -5245,10 +5878,13 @@
         <v>2</v>
       </c>
       <c r="G211">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="212" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H211">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="212" spans="1:8">
       <c r="A212">
         <v>133650</v>
       </c>
@@ -5268,10 +5904,13 @@
         <v>1</v>
       </c>
       <c r="G212">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="213" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H212">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="213" spans="1:8">
       <c r="A213">
         <v>131469</v>
       </c>
@@ -5291,10 +5930,13 @@
         <v>1</v>
       </c>
       <c r="G213">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="214" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H213">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="214" spans="1:8">
       <c r="A214">
         <v>131469</v>
       </c>
@@ -5314,10 +5956,13 @@
         <v>1</v>
       </c>
       <c r="G214">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="215" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H214">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="215" spans="1:8">
       <c r="A215">
         <v>131520</v>
       </c>
@@ -5337,10 +5982,13 @@
         <v>1</v>
       </c>
       <c r="G215">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="216" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H215">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="216" spans="1:8">
       <c r="A216">
         <v>131520</v>
       </c>
@@ -5360,10 +6008,13 @@
         <v>2</v>
       </c>
       <c r="G216">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="217" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H216">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="217" spans="1:8">
       <c r="A217">
         <v>131159</v>
       </c>
@@ -5383,10 +6034,13 @@
         <v>2</v>
       </c>
       <c r="G217">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="218" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H217">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="218" spans="1:8">
       <c r="A218">
         <v>131159</v>
       </c>
@@ -5406,10 +6060,13 @@
         <v>3</v>
       </c>
       <c r="G218">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="219" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H218">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="219" spans="1:8">
       <c r="A219">
         <v>131283</v>
       </c>
@@ -5429,10 +6086,13 @@
         <v>0</v>
       </c>
       <c r="G219">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="220" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H219">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="220" spans="1:8">
       <c r="A220">
         <v>131283</v>
       </c>
@@ -5452,10 +6112,13 @@
         <v>0</v>
       </c>
       <c r="G220">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="221" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H220">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="221" spans="1:8">
       <c r="A221">
         <v>130934</v>
       </c>
@@ -5475,10 +6138,13 @@
         <v>0</v>
       </c>
       <c r="G221">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="222" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H221">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="222" spans="1:8">
       <c r="A222">
         <v>130943</v>
       </c>
@@ -5498,10 +6164,13 @@
         <v>1</v>
       </c>
       <c r="G222">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="223" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H222">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="223" spans="1:8">
       <c r="A223">
         <v>130943</v>
       </c>
@@ -5521,10 +6190,13 @@
         <v>1</v>
       </c>
       <c r="G223">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="224" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H223">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="224" spans="1:8">
       <c r="A224">
         <v>130697</v>
       </c>
@@ -5544,10 +6216,13 @@
         <v>0</v>
       </c>
       <c r="G224">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="225" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H224">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="225" spans="1:8">
       <c r="A225">
         <v>130697</v>
       </c>
@@ -5567,10 +6242,13 @@
         <v>0</v>
       </c>
       <c r="G225">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="226" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H225">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="226" spans="1:8">
       <c r="A226">
         <v>130794</v>
       </c>
@@ -5590,10 +6268,13 @@
         <v>2</v>
       </c>
       <c r="G226">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="227" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H226">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="227" spans="1:8">
       <c r="A227">
         <v>130794</v>
       </c>
@@ -5613,10 +6294,13 @@
         <v>2</v>
       </c>
       <c r="G227">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="228" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H227">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="228" spans="1:8">
       <c r="A228">
         <v>128902</v>
       </c>
@@ -5636,10 +6320,13 @@
         <v>0</v>
       </c>
       <c r="G228">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="229" spans="1:7">
+        <v>2</v>
+      </c>
+      <c r="H228">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="229" spans="1:8">
       <c r="A229">
         <v>129020</v>
       </c>
@@ -5659,10 +6346,13 @@
         <v>0</v>
       </c>
       <c r="G229">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="230" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H229">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="230" spans="1:8">
       <c r="A230">
         <v>129020</v>
       </c>
@@ -5682,10 +6372,13 @@
         <v>0</v>
       </c>
       <c r="G230">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="231" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H230">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="231" spans="1:8">
       <c r="A231">
         <v>127060</v>
       </c>
@@ -5705,10 +6398,13 @@
         <v>0</v>
       </c>
       <c r="G231">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="232" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H231">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="232" spans="1:8">
       <c r="A232">
         <v>127060</v>
       </c>
@@ -5728,10 +6424,13 @@
         <v>0</v>
       </c>
       <c r="G232">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="233" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H232">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="233" spans="1:8">
       <c r="A233">
         <v>126775</v>
       </c>
@@ -5751,10 +6450,13 @@
         <v>0</v>
       </c>
       <c r="G233">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="234" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H233">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="234" spans="1:8">
       <c r="A234">
         <v>126818</v>
       </c>
@@ -5774,10 +6476,13 @@
         <v>2</v>
       </c>
       <c r="G234">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="235" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H234">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="235" spans="1:8">
       <c r="A235">
         <v>126818</v>
       </c>
@@ -5797,10 +6502,13 @@
         <v>0</v>
       </c>
       <c r="G235">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="236" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H235">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="236" spans="1:8">
       <c r="A236">
         <v>126580</v>
       </c>
@@ -5820,10 +6528,13 @@
         <v>0</v>
       </c>
       <c r="G236">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="237" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H236">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="237" spans="1:8">
       <c r="A237">
         <v>126614</v>
       </c>
@@ -5843,10 +6554,13 @@
         <v>2</v>
       </c>
       <c r="G237">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="238" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H237">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="238" spans="1:8">
       <c r="A238">
         <v>126614</v>
       </c>
@@ -5866,10 +6580,13 @@
         <v>0</v>
       </c>
       <c r="G238">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="239" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H238">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="239" spans="1:8">
       <c r="A239">
         <v>123961</v>
       </c>
@@ -5889,10 +6606,13 @@
         <v>0</v>
       </c>
       <c r="G239">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="240" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H239">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="240" spans="1:8">
       <c r="A240">
         <v>123961</v>
       </c>
@@ -5912,10 +6632,13 @@
         <v>0</v>
       </c>
       <c r="G240">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="241" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H240">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="241" spans="1:8">
       <c r="A241">
         <v>122755</v>
       </c>
@@ -5935,10 +6658,13 @@
         <v>0</v>
       </c>
       <c r="G241">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="242" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H241">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="242" spans="1:8">
       <c r="A242">
         <v>122597</v>
       </c>
@@ -5958,10 +6684,13 @@
         <v>1</v>
       </c>
       <c r="G242">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="243" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H242">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="243" spans="1:8">
       <c r="A243">
         <v>122409</v>
       </c>
@@ -5981,10 +6710,13 @@
         <v>0</v>
       </c>
       <c r="G243">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="244" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H243">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="244" spans="1:8">
       <c r="A244">
         <v>110680</v>
       </c>
@@ -6004,10 +6736,13 @@
         <v>2</v>
       </c>
       <c r="G244">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="245" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H244">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="245" spans="1:8">
       <c r="A245">
         <v>110680</v>
       </c>
@@ -6027,10 +6762,13 @@
         <v>1</v>
       </c>
       <c r="G245">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="246" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H245">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="246" spans="1:8">
       <c r="A246">
         <v>110705</v>
       </c>
@@ -6050,10 +6788,13 @@
         <v>2</v>
       </c>
       <c r="G246">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="247" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H246">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="247" spans="1:8">
       <c r="A247">
         <v>110705</v>
       </c>
@@ -6073,10 +6814,13 @@
         <v>1</v>
       </c>
       <c r="G247">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="248" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H247">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="248" spans="1:8">
       <c r="A248">
         <v>110714</v>
       </c>
@@ -6096,10 +6840,13 @@
         <v>4</v>
       </c>
       <c r="G248">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="249" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H248">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="249" spans="1:8">
       <c r="A249">
         <v>110714</v>
       </c>
@@ -6119,10 +6866,13 @@
         <v>2</v>
       </c>
       <c r="G249">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="250" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H249">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="250" spans="1:8">
       <c r="A250">
         <v>110653</v>
       </c>
@@ -6142,10 +6892,13 @@
         <v>1</v>
       </c>
       <c r="G250">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="251" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H250">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="251" spans="1:8">
       <c r="A251">
         <v>110662</v>
       </c>
@@ -6165,10 +6918,13 @@
         <v>2</v>
       </c>
       <c r="G251">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="252" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H251">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="252" spans="1:8">
       <c r="A252">
         <v>110662</v>
       </c>
@@ -6188,10 +6944,13 @@
         <v>2</v>
       </c>
       <c r="G252">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="253" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H252">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="253" spans="1:8">
       <c r="A253">
         <v>110671</v>
       </c>
@@ -6211,10 +6970,13 @@
         <v>3</v>
       </c>
       <c r="G253">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="254" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H253">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="254" spans="1:8">
       <c r="A254">
         <v>110671</v>
       </c>
@@ -6234,10 +6996,13 @@
         <v>1</v>
       </c>
       <c r="G254">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="255" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H254">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="255" spans="1:8">
       <c r="A255">
         <v>110635</v>
       </c>
@@ -6257,10 +7022,13 @@
         <v>5</v>
       </c>
       <c r="G255">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="256" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H255">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="256" spans="1:8">
       <c r="A256">
         <v>110635</v>
       </c>
@@ -6280,10 +7048,13 @@
         <v>2</v>
       </c>
       <c r="G256">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="257" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H256">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="257" spans="1:8">
       <c r="A257">
         <v>110644</v>
       </c>
@@ -6303,10 +7074,13 @@
         <v>1</v>
       </c>
       <c r="G257">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="258" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H257">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="258" spans="1:8">
       <c r="A258">
         <v>110644</v>
       </c>
@@ -6326,10 +7100,13 @@
         <v>2</v>
       </c>
       <c r="G258">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="259" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H258">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="259" spans="1:8">
       <c r="A259">
         <v>110653</v>
       </c>
@@ -6349,10 +7126,13 @@
         <v>2</v>
       </c>
       <c r="G259">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="260" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H259">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="260" spans="1:8">
       <c r="A260">
         <v>110592</v>
       </c>
@@ -6372,10 +7152,13 @@
         <v>1</v>
       </c>
       <c r="G260">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="261" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H260">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="261" spans="1:8">
       <c r="A261">
         <v>110608</v>
       </c>
@@ -6395,10 +7178,13 @@
         <v>0</v>
       </c>
       <c r="G261">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="262" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H261">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="262" spans="1:8">
       <c r="A262">
         <v>110556</v>
       </c>
@@ -6418,10 +7204,13 @@
         <v>1</v>
       </c>
       <c r="G262">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="263" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H262">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="263" spans="1:8">
       <c r="A263">
         <v>110565</v>
       </c>
@@ -6441,10 +7230,13 @@
         <v>0</v>
       </c>
       <c r="G263">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="264" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H263">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="264" spans="1:8">
       <c r="A264">
         <v>110583</v>
       </c>
@@ -6464,10 +7256,13 @@
         <v>0</v>
       </c>
       <c r="G264">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="265" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H264">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="265" spans="1:8">
       <c r="A265">
         <v>110404</v>
       </c>
@@ -6487,10 +7282,13 @@
         <v>0</v>
       </c>
       <c r="G265">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="266" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H265">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="266" spans="1:8">
       <c r="A266">
         <v>110404</v>
       </c>
@@ -6510,10 +7308,13 @@
         <v>2</v>
       </c>
       <c r="G266">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="267" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H266">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="267" spans="1:8">
       <c r="A267">
         <v>106397</v>
       </c>
@@ -6533,10 +7334,13 @@
         <v>0</v>
       </c>
       <c r="G267">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="268" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H267">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="268" spans="1:8">
       <c r="A268">
         <v>106397</v>
       </c>
@@ -6556,10 +7360,13 @@
         <v>0</v>
       </c>
       <c r="G268">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="269" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H268">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="269" spans="1:8">
       <c r="A269">
         <v>104179</v>
       </c>
@@ -6579,10 +7386,13 @@
         <v>4</v>
       </c>
       <c r="G269">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="270" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H269">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="270" spans="1:8">
       <c r="A270">
         <v>104179</v>
       </c>
@@ -6602,10 +7412,13 @@
         <v>0</v>
       </c>
       <c r="G270">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="271" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H270">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="271" spans="1:8">
       <c r="A271">
         <v>102614</v>
       </c>
@@ -6625,10 +7438,13 @@
         <v>2</v>
       </c>
       <c r="G271">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="272" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H271">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="272" spans="1:8">
       <c r="A272">
         <v>104151</v>
       </c>
@@ -6648,10 +7464,13 @@
         <v>1</v>
       </c>
       <c r="G272">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="273" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H272">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="273" spans="1:8">
       <c r="A273">
         <v>104151</v>
       </c>
@@ -6671,10 +7490,13 @@
         <v>1</v>
       </c>
       <c r="G273">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="274" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H273">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="274" spans="1:8">
       <c r="A274">
         <v>102614</v>
       </c>
@@ -6694,10 +7516,13 @@
         <v>0</v>
       </c>
       <c r="G274">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="275" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H274">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="275" spans="1:8">
       <c r="A275">
         <v>100858</v>
       </c>
@@ -6717,10 +7542,13 @@
         <v>0</v>
       </c>
       <c r="G275">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="276" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H275">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="276" spans="1:8">
       <c r="A276">
         <v>100858</v>
       </c>
@@ -6740,10 +7568,13 @@
         <v>0</v>
       </c>
       <c r="G276">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="277" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H276">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="277" spans="1:8">
       <c r="A277">
         <v>204857</v>
       </c>
@@ -6763,10 +7594,13 @@
         <v>1</v>
       </c>
       <c r="G277">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="278" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H277">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="278" spans="1:8">
       <c r="A278">
         <v>204857</v>
       </c>
@@ -6786,10 +7620,13 @@
         <v>1</v>
       </c>
       <c r="G278">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="279" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H278">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="279" spans="1:8">
       <c r="A279">
         <v>100751</v>
       </c>
@@ -6809,10 +7646,13 @@
         <v>1</v>
       </c>
       <c r="G279">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="280" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H279">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="280" spans="1:8">
       <c r="A280">
         <v>100751</v>
       </c>
@@ -6832,10 +7672,13 @@
         <v>1</v>
       </c>
       <c r="G280">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="281" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H280">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="281" spans="1:8">
       <c r="A281">
         <v>204796</v>
       </c>
@@ -6855,10 +7698,13 @@
         <v>5</v>
       </c>
       <c r="G281">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="282" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H281">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="282" spans="1:8">
       <c r="A282">
         <v>206084</v>
       </c>
@@ -6878,10 +7724,13 @@
         <v>2</v>
       </c>
       <c r="G282">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="283" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H282">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="283" spans="1:8">
       <c r="A283">
         <v>206084</v>
       </c>
@@ -6901,10 +7750,13 @@
         <v>0</v>
       </c>
       <c r="G283">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="284" spans="1:7">
+        <v>2</v>
+      </c>
+      <c r="H283">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="284" spans="1:8">
       <c r="A284">
         <v>206084</v>
       </c>
@@ -6924,10 +7776,13 @@
         <v>1</v>
       </c>
       <c r="G284">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="285" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H284">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="285" spans="1:8">
       <c r="A285">
         <v>206084</v>
       </c>
@@ -6947,10 +7802,13 @@
         <v>0</v>
       </c>
       <c r="G285">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="286" spans="1:7">
+        <v>2</v>
+      </c>
+      <c r="H285">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="286" spans="1:8">
       <c r="A286">
         <v>206941</v>
       </c>
@@ -6970,10 +7828,13 @@
         <v>1</v>
       </c>
       <c r="G286">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="287" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H286">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="287" spans="1:8">
       <c r="A287">
         <v>206604</v>
       </c>
@@ -6993,10 +7854,13 @@
         <v>0</v>
       </c>
       <c r="G287">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="288" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H287">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="288" spans="1:8">
       <c r="A288">
         <v>207388</v>
       </c>
@@ -7016,10 +7880,13 @@
         <v>1</v>
       </c>
       <c r="G288">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="289" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H288">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="289" spans="1:8">
       <c r="A289">
         <v>207388</v>
       </c>
@@ -7039,10 +7906,13 @@
         <v>0</v>
       </c>
       <c r="G289">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="290" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H289">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="290" spans="1:8">
       <c r="A290">
         <v>207500</v>
       </c>
@@ -7062,10 +7932,13 @@
         <v>1</v>
       </c>
       <c r="G290">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="291" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H290">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="291" spans="1:8">
       <c r="A291">
         <v>207500</v>
       </c>
@@ -7085,10 +7958,13 @@
         <v>1</v>
       </c>
       <c r="G291">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="292" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H291">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="292" spans="1:8">
       <c r="A292">
         <v>209551</v>
       </c>
@@ -7108,10 +7984,13 @@
         <v>0</v>
       </c>
       <c r="G292">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="293" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H292">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="293" spans="1:8">
       <c r="A293">
         <v>209542</v>
       </c>
@@ -7131,10 +8010,13 @@
         <v>0</v>
       </c>
       <c r="G293">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="294" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H293">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="294" spans="1:8">
       <c r="A294">
         <v>209542</v>
       </c>
@@ -7154,10 +8036,13 @@
         <v>0</v>
       </c>
       <c r="G294">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="295" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H294">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="295" spans="1:8">
       <c r="A295">
         <v>209551</v>
       </c>
@@ -7177,10 +8062,13 @@
         <v>1</v>
       </c>
       <c r="G295">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="296" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H295">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="296" spans="1:8">
       <c r="A296">
         <v>209807</v>
       </c>
@@ -7200,10 +8088,13 @@
         <v>0</v>
       </c>
       <c r="G296">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="297" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H296">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="297" spans="1:8">
       <c r="A297">
         <v>211273</v>
       </c>
@@ -7223,10 +8114,13 @@
         <v>0</v>
       </c>
       <c r="G297">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="298" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H297">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="298" spans="1:8">
       <c r="A298">
         <v>211440</v>
       </c>
@@ -7246,10 +8140,13 @@
         <v>1</v>
       </c>
       <c r="G298">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="299" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H298">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="299" spans="1:8">
       <c r="A299">
         <v>211440</v>
       </c>
@@ -7269,10 +8166,13 @@
         <v>1</v>
       </c>
       <c r="G299">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="300" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H299">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="300" spans="1:8">
       <c r="A300">
         <v>213543</v>
       </c>
@@ -7292,10 +8192,13 @@
         <v>1</v>
       </c>
       <c r="G300">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="301" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H300">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="301" spans="1:8">
       <c r="A301">
         <v>213020</v>
       </c>
@@ -7315,10 +8218,13 @@
         <v>2</v>
       </c>
       <c r="G301">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="302" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H301">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="302" spans="1:8">
       <c r="A302">
         <v>213543</v>
       </c>
@@ -7338,10 +8244,13 @@
         <v>1</v>
       </c>
       <c r="G302">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="303" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H302">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="303" spans="1:8">
       <c r="A303">
         <v>214777</v>
       </c>
@@ -7361,10 +8270,13 @@
         <v>2</v>
       </c>
       <c r="G303">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="304" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H303">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="304" spans="1:8">
       <c r="A304">
         <v>215062</v>
       </c>
@@ -7384,10 +8296,13 @@
         <v>1</v>
       </c>
       <c r="G304">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="305" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H304">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="305" spans="1:8">
       <c r="A305">
         <v>214777</v>
       </c>
@@ -7407,10 +8322,13 @@
         <v>2</v>
       </c>
       <c r="G305">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="306" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H305">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="306" spans="1:8">
       <c r="A306">
         <v>215293</v>
       </c>
@@ -7430,10 +8348,13 @@
         <v>1</v>
       </c>
       <c r="G306">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="307" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H306">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="307" spans="1:8">
       <c r="A307">
         <v>215293</v>
       </c>
@@ -7453,10 +8374,13 @@
         <v>2</v>
       </c>
       <c r="G307">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="308" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H307">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="308" spans="1:8">
       <c r="A308">
         <v>215062</v>
       </c>
@@ -7476,10 +8400,13 @@
         <v>3</v>
       </c>
       <c r="G308">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="309" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H308">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="309" spans="1:8">
       <c r="A309">
         <v>216339</v>
       </c>
@@ -7499,10 +8426,13 @@
         <v>1</v>
       </c>
       <c r="G309">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="310" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H309">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="310" spans="1:8">
       <c r="A310">
         <v>217156</v>
       </c>
@@ -7522,10 +8452,13 @@
         <v>4</v>
       </c>
       <c r="G310">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="311" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H310">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="311" spans="1:8">
       <c r="A311">
         <v>217156</v>
       </c>
@@ -7545,10 +8478,13 @@
         <v>2</v>
       </c>
       <c r="G311">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="312" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H311">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="312" spans="1:8">
       <c r="A312">
         <v>217484</v>
       </c>
@@ -7568,10 +8504,13 @@
         <v>0</v>
       </c>
       <c r="G312">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="313" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H312">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="313" spans="1:8">
       <c r="A313">
         <v>217882</v>
       </c>
@@ -7591,10 +8530,13 @@
         <v>0</v>
       </c>
       <c r="G313">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="314" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H313">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="314" spans="1:8">
       <c r="A314">
         <v>217484</v>
       </c>
@@ -7614,10 +8556,13 @@
         <v>0</v>
       </c>
       <c r="G314">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="315" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H314">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="315" spans="1:8">
       <c r="A315">
         <v>217882</v>
       </c>
@@ -7637,10 +8582,13 @@
         <v>0</v>
       </c>
       <c r="G315">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="316" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H315">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="316" spans="1:8">
       <c r="A316">
         <v>218663</v>
       </c>
@@ -7660,10 +8608,13 @@
         <v>0</v>
       </c>
       <c r="G316">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="317" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H316">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="317" spans="1:8">
       <c r="A317">
         <v>218663</v>
       </c>
@@ -7683,10 +8634,13 @@
         <v>1</v>
       </c>
       <c r="G317">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="318" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H317">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="318" spans="1:8">
       <c r="A318">
         <v>220181</v>
       </c>
@@ -7706,10 +8660,13 @@
         <v>2</v>
       </c>
       <c r="G318">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="319" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H318">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="319" spans="1:8">
       <c r="A319">
         <v>220862</v>
       </c>
@@ -7729,10 +8686,13 @@
         <v>0</v>
       </c>
       <c r="G319">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="320" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H319">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="320" spans="1:8">
       <c r="A320">
         <v>221759</v>
       </c>
@@ -7752,10 +8712,13 @@
         <v>0</v>
       </c>
       <c r="G320">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="321" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H320">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="321" spans="1:8">
       <c r="A321">
         <v>221999</v>
       </c>
@@ -7775,10 +8738,13 @@
         <v>2</v>
       </c>
       <c r="G321">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="322" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H321">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="322" spans="1:8">
       <c r="A322">
         <v>221999</v>
       </c>
@@ -7798,10 +8764,13 @@
         <v>0</v>
       </c>
       <c r="G322">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="323" spans="1:7">
+        <v>2</v>
+      </c>
+      <c r="H322">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="323" spans="1:8">
       <c r="A323">
         <v>221999</v>
       </c>
@@ -7821,10 +8790,13 @@
         <v>0</v>
       </c>
       <c r="G323">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="324" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H323">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="324" spans="1:8">
       <c r="A324">
         <v>221999</v>
       </c>
@@ -7844,10 +8816,13 @@
         <v>0</v>
       </c>
       <c r="G324">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="325" spans="1:7">
+        <v>2</v>
+      </c>
+      <c r="H324">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="325" spans="1:8">
       <c r="A325">
         <v>221759</v>
       </c>
@@ -7867,10 +8842,13 @@
         <v>0</v>
       </c>
       <c r="G325">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="326" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H325">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="326" spans="1:8">
       <c r="A326">
         <v>223232</v>
       </c>
@@ -7890,10 +8868,13 @@
         <v>0</v>
       </c>
       <c r="G326">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="327" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H326">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="327" spans="1:8">
       <c r="A327">
         <v>224554</v>
       </c>
@@ -7913,10 +8894,13 @@
         <v>1</v>
       </c>
       <c r="G327">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="328" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H327">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="328" spans="1:8">
       <c r="A328">
         <v>225511</v>
       </c>
@@ -7936,10 +8920,13 @@
         <v>1</v>
       </c>
       <c r="G328">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="329" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H328">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="329" spans="1:8">
       <c r="A329">
         <v>225511</v>
       </c>
@@ -7959,10 +8946,13 @@
         <v>1</v>
       </c>
       <c r="G329">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="330" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H329">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="330" spans="1:8">
       <c r="A330">
         <v>227216</v>
       </c>
@@ -7982,10 +8972,13 @@
         <v>0</v>
       </c>
       <c r="G330">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="331" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H330">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="331" spans="1:8">
       <c r="A331">
         <v>227757</v>
       </c>
@@ -8005,10 +8998,13 @@
         <v>0</v>
       </c>
       <c r="G331">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="332" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H331">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="332" spans="1:8">
       <c r="A332">
         <v>227757</v>
       </c>
@@ -8028,10 +9024,13 @@
         <v>2</v>
       </c>
       <c r="G332">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="333" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H332">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="333" spans="1:8">
       <c r="A333">
         <v>227216</v>
       </c>
@@ -8051,10 +9050,13 @@
         <v>1</v>
       </c>
       <c r="G333">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="334" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H333">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="334" spans="1:8">
       <c r="A334">
         <v>227881</v>
       </c>
@@ -8074,10 +9076,13 @@
         <v>0</v>
       </c>
       <c r="G334">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="335" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H334">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="335" spans="1:8">
       <c r="A335">
         <v>228246</v>
       </c>
@@ -8097,10 +9102,13 @@
         <v>1</v>
       </c>
       <c r="G335">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="336" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H335">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="336" spans="1:8">
       <c r="A336">
         <v>228246</v>
       </c>
@@ -8120,10 +9128,13 @@
         <v>0</v>
       </c>
       <c r="G336">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="337" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H336">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="337" spans="1:8">
       <c r="A337">
         <v>228459</v>
       </c>
@@ -8143,10 +9154,13 @@
         <v>0</v>
       </c>
       <c r="G337">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="338" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H337">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="338" spans="1:8">
       <c r="A338">
         <v>228431</v>
       </c>
@@ -8166,10 +9180,13 @@
         <v>0</v>
       </c>
       <c r="G338">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="339" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H338">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="339" spans="1:8">
       <c r="A339">
         <v>228769</v>
       </c>
@@ -8189,10 +9206,13 @@
         <v>0</v>
       </c>
       <c r="G339">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="340" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H339">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="340" spans="1:8">
       <c r="A340">
         <v>228796</v>
       </c>
@@ -8212,10 +9232,13 @@
         <v>0</v>
       </c>
       <c r="G340">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="341" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H340">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="341" spans="1:8">
       <c r="A341">
         <v>228723</v>
       </c>
@@ -8235,10 +9258,13 @@
         <v>1</v>
       </c>
       <c r="G341">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="342" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H341">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="342" spans="1:8">
       <c r="A342">
         <v>228723</v>
       </c>
@@ -8258,10 +9284,13 @@
         <v>1</v>
       </c>
       <c r="G342">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="343" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H342">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="343" spans="1:8">
       <c r="A343">
         <v>228778</v>
       </c>
@@ -8281,10 +9310,13 @@
         <v>0</v>
       </c>
       <c r="G343">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="344" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H343">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="344" spans="1:8">
       <c r="A344">
         <v>228778</v>
       </c>
@@ -8304,10 +9336,13 @@
         <v>1</v>
       </c>
       <c r="G344">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="345" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H344">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="345" spans="1:8">
       <c r="A345">
         <v>228787</v>
       </c>
@@ -8327,10 +9362,13 @@
         <v>0</v>
       </c>
       <c r="G345">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="346" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H345">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="346" spans="1:8">
       <c r="A346">
         <v>228787</v>
       </c>
@@ -8350,10 +9388,13 @@
         <v>0</v>
       </c>
       <c r="G346">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="347" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H346">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="347" spans="1:8">
       <c r="A347">
         <v>228875</v>
       </c>
@@ -8373,10 +9414,13 @@
         <v>0</v>
       </c>
       <c r="G347">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="348" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H347">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="348" spans="1:8">
       <c r="A348">
         <v>229115</v>
       </c>
@@ -8396,10 +9440,13 @@
         <v>2</v>
       </c>
       <c r="G348">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="349" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H348">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="349" spans="1:8">
       <c r="A349">
         <v>229115</v>
       </c>
@@ -8419,10 +9466,13 @@
         <v>0</v>
       </c>
       <c r="G349">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="350" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H349">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="350" spans="1:8">
       <c r="A350">
         <v>230038</v>
       </c>
@@ -8442,10 +9492,13 @@
         <v>0</v>
       </c>
       <c r="G350">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="351" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H350">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="351" spans="1:8">
       <c r="A351">
         <v>230038</v>
       </c>
@@ -8465,10 +9518,13 @@
         <v>0</v>
       </c>
       <c r="G351">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="352" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H351">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="352" spans="1:8">
       <c r="A352">
         <v>230764</v>
       </c>
@@ -8488,10 +9544,13 @@
         <v>2</v>
       </c>
       <c r="G352">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="353" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H352">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="353" spans="1:8">
       <c r="A353">
         <v>230764</v>
       </c>
@@ -8511,10 +9570,13 @@
         <v>1</v>
       </c>
       <c r="G353">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="354" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H353">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="354" spans="1:8">
       <c r="A354">
         <v>230728</v>
       </c>
@@ -8534,10 +9596,13 @@
         <v>0</v>
       </c>
       <c r="G354">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="355" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H354">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="355" spans="1:8">
       <c r="A355">
         <v>230728</v>
       </c>
@@ -8557,10 +9622,13 @@
         <v>0</v>
       </c>
       <c r="G355">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="356" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H355">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="356" spans="1:8">
       <c r="A356">
         <v>231174</v>
       </c>
@@ -8580,10 +9648,13 @@
         <v>0</v>
       </c>
       <c r="G356">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="357" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H356">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="357" spans="1:8">
       <c r="A357">
         <v>231624</v>
       </c>
@@ -8603,10 +9674,13 @@
         <v>4</v>
       </c>
       <c r="G357">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="358" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H357">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="358" spans="1:8">
       <c r="A358">
         <v>231624</v>
       </c>
@@ -8626,10 +9700,13 @@
         <v>1</v>
       </c>
       <c r="G358">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="359" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H358">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="359" spans="1:8">
       <c r="A359">
         <v>232265</v>
       </c>
@@ -8649,10 +9726,13 @@
         <v>0</v>
       </c>
       <c r="G359">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="360" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H359">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="360" spans="1:8">
       <c r="A360">
         <v>232265</v>
       </c>
@@ -8672,10 +9752,13 @@
         <v>1</v>
       </c>
       <c r="G360">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="361" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H360">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="361" spans="1:8">
       <c r="A361">
         <v>232982</v>
       </c>
@@ -8695,10 +9778,13 @@
         <v>1</v>
       </c>
       <c r="G361">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="362" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H361">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="362" spans="1:8">
       <c r="A362">
         <v>232982</v>
       </c>
@@ -8718,10 +9804,13 @@
         <v>2</v>
       </c>
       <c r="G362">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="363" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H362">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="363" spans="1:8">
       <c r="A363">
         <v>234030</v>
       </c>
@@ -8741,10 +9830,13 @@
         <v>0</v>
       </c>
       <c r="G363">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="364" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H363">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="364" spans="1:8">
       <c r="A364">
         <v>234076</v>
       </c>
@@ -8764,10 +9856,13 @@
         <v>6</v>
       </c>
       <c r="G364">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="365" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H364">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="365" spans="1:8">
       <c r="A365">
         <v>233921</v>
       </c>
@@ -8787,10 +9882,13 @@
         <v>0</v>
       </c>
       <c r="G365">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="366" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H365">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="366" spans="1:8">
       <c r="A366">
         <v>233921</v>
       </c>
@@ -8810,10 +9908,13 @@
         <v>0</v>
       </c>
       <c r="G366">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="367" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H366">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="367" spans="1:8">
       <c r="A367">
         <v>234076</v>
       </c>
@@ -8833,10 +9934,13 @@
         <v>3</v>
       </c>
       <c r="G367">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="368" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H367">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="368" spans="1:8">
       <c r="A368">
         <v>236948</v>
       </c>
@@ -8856,10 +9960,13 @@
         <v>7</v>
       </c>
       <c r="G368">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="369" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H368">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="369" spans="1:8">
       <c r="A369">
         <v>236948</v>
       </c>
@@ -8879,10 +9986,13 @@
         <v>2</v>
       </c>
       <c r="G369">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="370" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H369">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="370" spans="1:8">
       <c r="A370">
         <v>236939</v>
       </c>
@@ -8902,10 +10012,13 @@
         <v>0</v>
       </c>
       <c r="G370">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="371" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H370">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="371" spans="1:8">
       <c r="A371">
         <v>236939</v>
       </c>
@@ -8925,10 +10038,13 @@
         <v>0</v>
       </c>
       <c r="G371">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="372" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H371">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="372" spans="1:8">
       <c r="A372">
         <v>238032</v>
       </c>
@@ -8948,10 +10064,13 @@
         <v>5</v>
       </c>
       <c r="G372">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="373" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H372">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="373" spans="1:8">
       <c r="A373">
         <v>238032</v>
       </c>
@@ -8971,10 +10090,13 @@
         <v>0</v>
       </c>
       <c r="G373">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="374" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H373">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="374" spans="1:8">
       <c r="A374">
         <v>240365</v>
       </c>
@@ -8994,10 +10116,13 @@
         <v>0</v>
       </c>
       <c r="G374">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="375" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H374">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="375" spans="1:8">
       <c r="A375">
         <v>240444</v>
       </c>
@@ -9017,10 +10142,13 @@
         <v>1</v>
       </c>
       <c r="G375">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="376" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H375">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="376" spans="1:8">
       <c r="A376">
         <v>240453</v>
       </c>
@@ -9040,10 +10168,13 @@
         <v>0</v>
       </c>
       <c r="G376">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="377" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H376">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="377" spans="1:8">
       <c r="A377">
         <v>240444</v>
       </c>
@@ -9063,10 +10194,13 @@
         <v>2</v>
       </c>
       <c r="G377">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="378" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H377">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="378" spans="1:8">
       <c r="A378">
         <v>240727</v>
       </c>
@@ -9086,10 +10220,13 @@
         <v>1</v>
       </c>
       <c r="G378">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="379" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H378">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="379" spans="1:8">
       <c r="A379">
         <v>240727</v>
       </c>
@@ -9109,10 +10246,13 @@
         <v>1</v>
       </c>
       <c r="G379">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="380" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H379">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="380" spans="1:8">
       <c r="A380">
         <v>240453</v>
       </c>
@@ -9132,10 +10272,13 @@
         <v>1</v>
       </c>
       <c r="G380">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="381" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H380">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="381" spans="1:8">
       <c r="A381">
         <v>243197</v>
       </c>
@@ -9155,10 +10298,13 @@
         <v>1</v>
       </c>
       <c r="G381">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="382" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H381">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="382" spans="1:8">
       <c r="A382">
         <v>243221</v>
       </c>
@@ -9178,10 +10324,13 @@
         <v>0</v>
       </c>
       <c r="G382">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="383" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H382">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="383" spans="1:8">
       <c r="A383">
         <v>243744</v>
       </c>
@@ -9201,10 +10350,13 @@
         <v>1</v>
       </c>
       <c r="G383">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="384" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H383">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="384" spans="1:8">
       <c r="A384">
         <v>243744</v>
       </c>
@@ -9224,10 +10376,13 @@
         <v>6</v>
       </c>
       <c r="G384">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="385" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H384">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="385" spans="1:8">
       <c r="A385">
         <v>243780</v>
       </c>
@@ -9247,10 +10402,13 @@
         <v>4</v>
       </c>
       <c r="G385">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="386" spans="1:7">
+        <v>1</v>
+      </c>
+      <c r="H385">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="386" spans="1:8">
       <c r="A386">
         <v>243780</v>
       </c>
@@ -9270,6 +10428,9 @@
         <v>0</v>
       </c>
       <c r="G386">
+        <v>1</v>
+      </c>
+      <c r="H386">
         <v>2001</v>
       </c>
     </row>
